--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -567,7 +567,7 @@
         <v>45888.42537037037</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45812.58784722222</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>46008</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46175.66145833334</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45468</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46008</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>45964.56922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45384.34295138889</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45294</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44958.56475694444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45081</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45490.76049768519</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44532</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45356.66606481482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>46147.57675925926</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45093.35027777778</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45392</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45545.68635416667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>44673</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>45978.4428587963</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45912.94699074074</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45995</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>44386</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45617</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45606.38186342592</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>46045.55876157407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45279</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45280</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45554.63932870371</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46161.62931712963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45544</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45824.44016203703</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45273</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>46182</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45098</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693.45207175926</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44812</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44458.3855787037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>44361</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44518.520625</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>44536.54855324074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>44764.50403935185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44434</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>44463.35908564815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44519.62116898148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44501</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44814</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44645.46194444445</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44438</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44446.36678240741</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44393</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44643</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44515.49590277778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44814.28984953704</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44480</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44525.97056712963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44578</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44516.59821759259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44803.73929398148</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>44470</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44466.59662037037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44400</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44721</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44739.4056712963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44590</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>44820.40541666667</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44814.31871527778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44442</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44769.63366898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44820</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44711.47668981482</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44474</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44880.28204861111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44495.62099537037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44508.56681712963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44599.68471064815</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44376.66452546296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44416.46971064815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44476</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44599.55104166667</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44389.50287037037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44651</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44876.69045138889</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44671</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44495</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44466.60013888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44496</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44397</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44396</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44750</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44379.55038194444</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44568.5809837963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44420.32788194445</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44427.65782407407</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44442.54784722222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44543.68087962963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44468.3096875</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44470.61033564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44613.36252314815</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44746.44984953704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44474.35017361111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44412</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44610.50777777778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44420.32596064815</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44610</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44491.5821875</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44740.66774305556</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44483</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44617.44428240741</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44426.68665509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44726.59372685185</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44468.50265046296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44551</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44393</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44599</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44457.87717592593</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44463</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44367.09428240741</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44645</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44781.45118055555</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44704.36118055556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44522.45008101852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44532.6606712963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44532.66989583334</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44498</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44439</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44860.45040509259</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44596</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44712</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44579</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44711.51280092593</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44438</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44769.88133101852</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44502.74899305555</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44452.39826388889</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44427.62268518518</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44483</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44508.40770833333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44434.37454861111</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44574.59645833333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44537.49590277778</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44537.56038194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44489.71826388889</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44487</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44490.64082175926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44603</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44596.66450231482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44406.50225694444</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44473</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44560.60773148148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44820.40097222223</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44474</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44820.40373842593</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44894</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44915</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44523.64958333333</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44802.50060185185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45386.86743055555</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45594.49429398148</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45594.49712962963</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45594.50039351852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45594.50556712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45594.50665509259</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45420.39758101852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45715</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45236.61423611111</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44573</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45477.36792824074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44967</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>45460.43055555555</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45672.47678240741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44502.76005787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45324.66358796296</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44537</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44764</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45517.49451388889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45594.49760416667</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45594.50193287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45594.50355324074</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45594.51657407408</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45554.61875</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45775.43115740741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45056.60450231482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45679.60483796296</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44988.31290509259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45534.56091435185</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45762.57912037037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45558.36578703704</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45702.38599537037</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45152.53986111111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45330</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44991</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44900.38261574074</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45219</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45057</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45322.43651620371</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45933.42581018519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44979.57680555555</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45161</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44676</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45240</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45937.48282407408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45937.46489583333</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44656</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44970.630625</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45181</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45121</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45121</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45121</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45222.56923611111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45397.59635416666</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45440.48216435185</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44713.535</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45754.5728125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45645.6278587963</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45622.47103009259</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45288.44112268519</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45229.49297453704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45896</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45692.56483796296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45278.47853009259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45028</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45937.47538194444</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45517.66657407407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44532</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45777.49614583333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45777.49822916667</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45194</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45816.46207175926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45033</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45547.67628472222</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45884.46983796296</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45777.49708333334</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44602.57952546296</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45519.66887731481</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45280.34100694444</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45225.5787037037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45127.42803240741</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45780.85372685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45780.85699074074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44620</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45478.56365740741</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45946.2662037037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45950.49357638889</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44880</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45561.66087962963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44894</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45923.67596064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45541.6099537037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45541.73261574074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44599</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44487</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45341.61912037037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45952.48637731482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45726.40159722222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45546</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44547</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45890.86472222222</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45219.41055555556</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45895.43204861111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45392</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45958.84930555556</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45894.42326388889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45315</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45946.66081018518</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45953.65040509259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45964.56096064814</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45114.70386574074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45783.50424768519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45856.43934027778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45782.65293981481</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45359.32828703704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45897.57736111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45964.43373842593</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45780.88527777778</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45555.57487268518</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45330</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45924.65366898148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45714.88269675926</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45105.37561342592</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45534.49916666667</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45784.56236111111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45579.62326388889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45557.57099537037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45810.60581018519</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45691</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45108.9196875</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45719.53642361111</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45645.62145833333</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45835.38336805555</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44781.4933912037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45971.51917824074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45902</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45902.6637962963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45905.56949074074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45642.37322916667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45557.51626157408</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45905.33540509259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45583.47736111111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45408.63730324074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45586.89740740741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45309.49473379629</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44854.4802199074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45211.85349537037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45737.55744212963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45614.37194444444</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45909.34719907407</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45716.88037037037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44909.78114583333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45686.44939814815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45233.37359953704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45608.57136574074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45309.48623842592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44705</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45973.47957175926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45789.63024305556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45253.57648148148</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44552.83320601852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45309.48236111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45244.79412037037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45244.871875</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45973.64590277777</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45911.7464699074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45975.37895833333</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45910.64783564815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45975.37184027778</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45787.28256944445</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45300.52561342593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44858.48517361111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>44814.29394675926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44814.30006944444</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45061</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45716.87329861111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45791.46324074074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45979.62671296296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45979.62482638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45979.70398148148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45980.61280092593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45280.34623842593</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45412.37150462963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45916.28979166667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44929</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45918.48403935185</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45372.83673611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44746.47082175926</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44896</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45918</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>44981</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45918</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45918</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45918</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45918</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45918</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45019.29746527778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45194</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45924.64648148148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45925.66645833333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45924.64511574074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45714.41549768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45924.36989583333</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45246.34271990741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45140.6528125</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45112</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45219.41693287037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45631.39725694444</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45993.45324074074</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45993.58273148148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>44959.48167824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45988.49306712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45995</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45999.4191087963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45995</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45168.88072916667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45397.60945601852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>46000.43627314815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44386</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45166.65635416667</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46001.90539351852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45623.63510416666</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45194.49377314815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45222.56635416667</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45244</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45162.43773148148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45162.44449074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45090.77837962963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>46007.70440972222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44679</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45128</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46008.51371527778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45611.70842592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>46010.49761574074</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46010.49818287037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>46010.52921296296</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45304</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46010.67133101852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45740.79685185185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44866.54954861111</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>46010.50359953703</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44529</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45686.59162037037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45686.60993055555</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45278.58283564815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>46019</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45111</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46019</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45245</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46029.47736111111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46029.48863425926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44678.43256944444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>44915.05086805556</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45797</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46031.40212962963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45104.61909722222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45796.48868055556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>46031.40054398148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44824.31822916667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45304.56362268519</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45574.47497685185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45190</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>46035.30069444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45279.67762731481</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45753.32603009259</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44426.54175925926</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>44741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>44537.56209490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45236.44059027778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45236.44439814815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45317.65170138889</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46035.35650462963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45638.33574074074</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45764</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45803.50699074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46035.31605324074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45121</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45121</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45121</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46036.31258101852</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44950.47614583333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>46036.41478009259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45169</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45036</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>46036.43053240741</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46036.66730324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45665.64802083333</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45921.70836805556</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46041.39274305556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45749.4678587963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45805</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45763.61952546296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46043.61449074074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45048</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>46045.64295138889</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>46045.44012731482</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45447.41306712963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45463.64552083334</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46049.65488425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45230.68856481482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>46048</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45240.63111111111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45154</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46049</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45715.3468287037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45328</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45328</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46049.65270833333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>46049.66483796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46051.66256944444</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45769.35501157407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45632.4446875</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45194.39922453704</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44922</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45812.48452546296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>46057.57069444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45446.37311342593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45058</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46056.45358796296</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46057.56871527778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>46056.45521990741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46057.5653587963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45817.70034722222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45818</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45281.69575231482</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46056.46550925926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45769.6050462963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45274.6619212963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45686.61557870371</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45611.95675925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>46059.36828703704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>46059.40028935186</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46059.37333333334</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45594.49349537037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45594.49548611111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45820.65064814815</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45820.49263888889</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45820.64496527778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45818</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45825.38452546296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45825.69231481481</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45281.62967592593</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>46061.39715277778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45824.47944444444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45824.48297453704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45827</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45030</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45210</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45831.53054398148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45112</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44966.305</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45831.4883912037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45387.50104166667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45560.46328703704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45091</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45832.87528935185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45715</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44687.60125</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>46073.59329861111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45436.46103009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45260.3800462963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46073.71484953703</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>46072.43777777778</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45148.54725694445</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45148</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44545.65563657408</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45805</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45091.38644675926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45390.55701388889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45124.58091435185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45385</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46075.80827546296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46079.35677083334</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46079.3521412037</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46084.52283564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>46084.4408912037</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46083.35065972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45835.45113425926</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45342.75077546296</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45835.45200231481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45049.41876157407</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45835.37918981481</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46083.50642361111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45244.87707175926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45629.45599537037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46083</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>46083.63700231481</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46083.56542824074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45599.3781712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45840.44729166666</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45145</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>46087.45732638889</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45540</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>44845</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45169.45532407407</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44711.68930555556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45846</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45153</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45846</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44938</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45847.5616087963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44434</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45104.60564814815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45702.59452546296</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45769.48512731482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45387.36863425926</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45113</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>46097</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45579</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45513.4027199074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45215</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44532</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44427</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46099.48590277778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46100.37087962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46100.34037037037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>46100.36679398148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>46099.45767361111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45224</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46100.63233796296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44641</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46100.34387731482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45390</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45853.69938657407</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45070.29650462963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45128</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45259</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45309.47016203704</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45309.48903935185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45488.29020833333</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45009</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46146.65170138889</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46146.65184027778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46146.65664351852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45686.33597222222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45103</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46147.6059837963</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46147.61996527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45253.58075231482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45250.30325231481</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46147.58696759259</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>46147.5946875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45016.62603009259</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45670</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>46147.5657175926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>46148.37179398148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45250.40770833333</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44397.68809027778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44986</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45740.59585648148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46108.42422453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46021</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>46021</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46021</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46021</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45183.5531712963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46021</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46021</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>46021</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46107.59799768519</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46107.60973379629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46108.49034722222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46149.67800925926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>44746</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>44977.63971064815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45114</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45114</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45296.33238425926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45181</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45090.5199537037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44867.6309375</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>46112.58732638889</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46112.59736111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45597.67458333333</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45401</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>44769.62064814815</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45685.42418981482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>44972.73002314815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>44769.61976851852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44928</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46112.41709490741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45568.34643518519</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>46153.60424768519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45061</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45267.31300925926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45384.34543981482</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>46113</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45097</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44904.33903935185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44904.34511574074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45420.39990740741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45782.63381944445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>45504.53853009259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45583</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46161.45658564815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45753.32285879629</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>46162.59923611111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46162.60908564815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>45617.72848379629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44872</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45594.6340625</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>44370</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>46162.59502314815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>44670</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>45594.50951388889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45594.63260416667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45324</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45029.47953703703</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46161.63166666667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>46161.63422453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44651</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46162.61810185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45719.54616898148</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45719</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44393</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45533.45201388889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46119.9412037037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45147</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46163.49306712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>46163.50744212963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>46163.51511574074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45874.42462962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45392.39776620371</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45392</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46163.49570601852</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45103</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45103</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45103.55109953704</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45350.33565972222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45247</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45559</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45579</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46163.49925925926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46163.50251157407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46163.51131944444</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45427</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45250.4330787037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45733.84600694444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46168.40664351852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45855.66106481481</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46125.55934027778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>46167.37201388889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>44552</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45180.44605324074</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45580.83032407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45883.58010416666</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44761</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45883.51181712963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45477.36865740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45190</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45559.33650462963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43953,7 +43953,7 @@
         <v>45153.31517361111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>46125.56210648148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>45421.62476851852</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45201</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>46168.40579861111</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>44424.56576388889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>44811.45271990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45113.57717592592</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46170.49400462963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45113</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46170.38807870371</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>44896</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46171.50009259259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45538</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>44903</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44502</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45754.66629629629</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>46170.49219907408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46171.30791666666</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46129.57209490741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46171.50685185185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45538.33878472223</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45301.65822916666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44595</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45330</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45250.41039351852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45281</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>44592.5402662037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45722.67716435185</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45557.57826388889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45432.55671296296</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>44686.44046296296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45400.47762731482</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>44705.44402777778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45315.56436342592</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>45065</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44743</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45121</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>44831.38086805555</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46134.52199074074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>45302.71091435185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45573.91921296297</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>44676.47767361111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45881.56177083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45036.60653935185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45302.71799768518</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46134.55832175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45632.45528935185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46134.53310185186</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45188.47006944445</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45552.57313657407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45181</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45071</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45558.67806712963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45594.49958333333</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45594.51133101852</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45594.51443287037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>46134.49333333333</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45677</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45582.78583333334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45923.38232638889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45693.34945601852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45764.57550925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45939.49226851852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45644.54353009259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45056.48001157407</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45037.5341087963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45581.55803240741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>44609</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>44652</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>44956.39506944444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45300.55637731482</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45211.82909722222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>44468</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45894.43885416666</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45923.58896990741</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45210.6784837963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45883.6346412037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45883.64103009259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45827.56438657407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45533.38872685185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>44986</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45638.51944444444</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45743</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45687.94340277778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45327</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>44741.5471412037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45338.5585300926</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45791.48850694444</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44960.58287037037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>44843.29655092592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45670</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45665.6562962963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45833.66576388889</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45782.64549768518</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>44874</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>44874.58840277778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45688.62399305555</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45909</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>44963</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45775.45998842592</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44600</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>45412.44925925926</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45412.45357638889</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45757.4737037037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45316</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45316.41688657407</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45551</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45835.3862962963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>44896</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45601.46222222222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45679.92653935185</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45316.42096064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45841.85952546296</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46139.65122685185</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45826</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45960.38902777778</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45140.49438657407</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45426</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45446</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45392.38908564814</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45166.48473379629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45905.32910879629</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45345.30666666666</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44915.74278935185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44972</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45463</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>44998</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45846</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45698.61065972222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45468.46099537037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>45827.5565162037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45874</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45818</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>44880.29931712963</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51765,7 +51765,7 @@
         <v>45676.75392361111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45810.66587962963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45127.38489583333</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45127</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45288.37354166667</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45022.55644675926</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>44869.55530092592</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>44998.41530092592</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>44522</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45217.47178240741</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>46183.44533564815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>46183.48128472222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45085.48240740741</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44609</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>44457.86240740741</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45329</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45686.5972800926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45722.95646990741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45560.44628472222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>44577.67608796297</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45419.61466435185</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>44831</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45611.70576388889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45679.49554398148</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45679.60159722222</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45030</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45300.54975694444</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45877.47127314815</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>44774.52144675926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45128.63200231481</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45128</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45111.55594907407</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45638.33728009259</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>46183.00041666667</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45386.86943287037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45165.53953703704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45533.63113425926</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>46183.55180555556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45555.60236111111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45141.33791666666</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45141</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>46183.54673611111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>44496</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45579.46674768518</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45754</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45754.568125</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45012.4278587963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45127</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44867.62049768519</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45552.70320601852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45247</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45511.58850694444</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>44922.87642361111</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45048</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45205</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>44501</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>44995</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>44876.69168981481</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45495.89736111111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>44963.87038194444</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45106.5721875</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45385.58976851852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>45385.59068287037</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>44900.54149305556</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>44473</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55552,7 +55552,7 @@
         <v>45199</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45070.29798611111</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>44494.60379629629</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>45754</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45224.33578703704</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>44711.39636574074</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>44782</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45572</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>45204</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45443.55731481482</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56184,7 +56184,7 @@
         <v>45726.34802083333</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>45139.7190625</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>45373.49592592593</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>44452.39638888889</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56412,7 +56412,7 @@
         <v>45369.61829861111</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56469,7 +56469,7 @@
         <v>45127.60962962963</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45127.61971064815</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45372</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56640,7 +56640,7 @@
         <v>45219</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>45594.50804398148</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45594.5128587963</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>44690.40230324074</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45385</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>45702.65407407407</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>45000</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45446.40025462963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>44858</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45594.49064814814</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45594.49494212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45594.49597222222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45594.49865740741</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45594.51395833334</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45594.51512731481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45302.78386574074</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45302.78486111111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>44959.48619212963</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>44894</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45267.60236111111</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45198</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44651</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45280</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>45509</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58053,7 +58053,7 @@
         <v>45369.66939814815</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>45447.35372685185</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>45378</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45495.70517361111</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58281,7 +58281,7 @@
         <v>45446.39304398148</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>45008.52043981481</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>44739.6016087963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45519.33865740741</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58509,7 +58509,7 @@
         <v>45176.58175925926</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58566,7 +58566,7 @@
         <v>45176.58371527777</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45644.62018518519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>44812</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>44992</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>45139.69394675926</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58851,7 +58851,7 @@
         <v>45244</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>44384</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>45232.63908564814</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>45705</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45078</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45737.55483796296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45108</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>44749</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45468.49049768518</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45127.43435185185</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45273</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45392.39731481481</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45608.43087962963</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>44894</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>44677.39790509259</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45763</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>45089.44758101852</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59840,7 +59840,7 @@
         <v>45236.6053587963</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
         <v>45392.39274305556</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59959,7 +59959,7 @@
         <v>45342.53827546296</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45189.70568287037</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45189.71008101852</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>44909.65577546296</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45190.38162037037</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45714.9666087963</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>44599.52814814815</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45614.61105324074</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>45692</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45384.80710648148</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45448.38922453704</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45294</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>45587</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>45219.45643518519</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>45147</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>44536.55450231482</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>44732</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45216.70546296296</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45198.33086805556</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44379.55199074074</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45644.57841435185</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45014</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61223,7 +61223,7 @@
         <v>44897</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45447.41501157408</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45649.6471875</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45014.55976851852</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>45743</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -567,7 +567,7 @@
         <v>45888.42537037037</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45812.58784722222</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>46008</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46175.66145833334</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45468</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46008</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>45964.56922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45384.34295138889</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45294</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44958.56475694444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45081</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45490.76049768519</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44532</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45356.66606481482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>46147.57675925926</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45093.35027777778</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45392</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45545.68635416667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>44673</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>45978.4428587963</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45912.94699074074</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45995</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>44386</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45643</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45617</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45606.38186342592</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>46045.55876157407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45279</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45280</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45554.63932870371</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46161.62931712963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45544</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45824.44016203703</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45273</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>46182</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45098</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693.45207175926</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44812</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44458.3855787037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>44361</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44518.520625</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>44536.54855324074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>44764.50403935185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44434</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>44463.35908564815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44519.62116898148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44501</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44814</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44645.46194444445</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44438</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44446.36678240741</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44393</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44643</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44515.49590277778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44814.28984953704</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44480</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44525.97056712963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44578</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44516.59821759259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44803.73929398148</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>44470</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44466.59662037037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44400</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44721</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44739.4056712963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44590</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>44820.40541666667</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44814.31871527778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44442</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44769.63366898148</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44820</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44711.47668981482</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44474</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44880.28204861111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44495.62099537037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44508.56681712963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44599.68471064815</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44376.66452546296</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44416.46971064815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44476</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44599.55104166667</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44389.50287037037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44651</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44876.69045138889</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44671</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44495</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44466.60013888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44496</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44397</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44396</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44750</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44379.55038194444</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44568.5809837963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44420.32788194445</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44427.65782407407</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44442.54784722222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44543.68087962963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44426</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44468.3096875</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44470.61033564815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44613.36252314815</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44746.44984953704</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44474.35017361111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44412</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44610.50777777778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44420.32596064815</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44610</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44491.5821875</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44740.66774305556</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44483</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44617.44428240741</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44426.68665509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44726.59372685185</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44468.50265046296</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44551</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44393</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44599</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44457.87717592593</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44463</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44367.09428240741</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44645</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44781.45118055555</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44704.36118055556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44522.45008101852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44532.6606712963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44532.66989583334</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44498</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44439</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44860.45040509259</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44596</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44712</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44579</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44711.51280092593</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44438</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44769.88133101852</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44502.74899305555</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44452.39826388889</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44427.62268518518</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44483</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44508.40770833333</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44434.37454861111</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44574.59645833333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44537.49590277778</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44537.56038194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44571</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44489.71826388889</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44487</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44490.64082175926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44603</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44596.66450231482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44406.50225694444</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44473</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44560.60773148148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44820.40097222223</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44474</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44820.40373842593</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44894</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44915</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44523.64958333333</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44802.50060185185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45386.86743055555</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45594.49429398148</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45594.49712962963</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45594.50039351852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45594.50556712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45594.50665509259</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45420.39758101852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45715</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45236.61423611111</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44573</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45477.36792824074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44967</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>45460.43055555555</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45672.47678240741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44502.76005787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45324.66358796296</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44537</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44764</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45517.49451388889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45594.49760416667</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>45594.50193287037</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45594.50355324074</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45594.51657407408</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45554.61875</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45775.43115740741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45056.60450231482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45679.60483796296</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44988.31290509259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45534.56091435185</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45762.57912037037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45558.36578703704</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45702.38599537037</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45152.53986111111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45330</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44991</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44900.38261574074</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45219</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45057</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45322.43651620371</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45933.42581018519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44979.57680555555</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45161</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44676</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45240</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45937.48282407408</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45937.46489583333</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44656</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44970.630625</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45181</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45121</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45121</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45121</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45222.56923611111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45397.59635416666</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45440.48216435185</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44713.535</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45754.5728125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45645.6278587963</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45622.47103009259</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45288.44112268519</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45229.49297453704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45896</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45692.56483796296</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45278.47853009259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45028</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45937.47538194444</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45517.66657407407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44532</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45777.49614583333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45777.49822916667</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45194</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45816.46207175926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45033</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45547.67628472222</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45884.46983796296</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45777.49708333334</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44602.57952546296</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45519.66887731481</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45280.34100694444</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45225.5787037037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45127.42803240741</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45780.85372685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45780.85699074074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44620</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45478.56365740741</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45946.2662037037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45950.49357638889</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44880</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45561.66087962963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44894</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45923.67596064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45541.6099537037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45541.73261574074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44599</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44487</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45341.61912037037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45952.48637731482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45726.40159722222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45546</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44547</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45890.86472222222</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45219.41055555556</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45895.43204861111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45392</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45958.84930555556</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45894.42326388889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45315</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45946.66081018518</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45953.65040509259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45964.56096064814</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45114.70386574074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45783.50424768519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45856.43934027778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45782.65293981481</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45359.32828703704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45897.57736111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45964.43373842593</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45780.88527777778</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45555.57487268518</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45330</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45924.65366898148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45714.88269675926</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45105.37561342592</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45534.49916666667</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45784.56236111111</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45579.62326388889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45557.57099537037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45810.60581018519</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45691</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45108.9196875</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45719.53642361111</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45645.62145833333</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45835.38336805555</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44781.4933912037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45971.51917824074</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45902</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45902.6637962963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45905.56949074074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45642.37322916667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45557.51626157408</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45905.33540509259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45583.47736111111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45408.63730324074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45586.89740740741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45309.49473379629</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44854.4802199074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45211.85349537037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45737.55744212963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45614.37194444444</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45909.34719907407</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45716.88037037037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44909.78114583333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45686.44939814815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45233.37359953704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45608.57136574074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45309.48623842592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44705</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45973.47957175926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45789.63024305556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45253.57648148148</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44552.83320601852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45309.48236111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45244.79412037037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45244.871875</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45973.64590277777</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45911.7464699074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45975.37895833333</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45910.64783564815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45975.37184027778</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45787.28256944445</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45300.52561342593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44858.48517361111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>44814.29394675926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44814.30006944444</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45061</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45716.87329861111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45791.46324074074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45979.62671296296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45979.62482638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45979.70398148148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45980.61280092593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45280.34623842593</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45412.37150462963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45916.28979166667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44929</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45918.48403935185</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45372.83673611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44746.47082175926</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44896</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45918</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>44981</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45918</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45918</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45918</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45918</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45918</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45019.29746527778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45194</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45924.64648148148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45925.66645833333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45924.64511574074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45714.41549768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45924.36989583333</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45246.34271990741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45140.6528125</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45112</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45219.41693287037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45631.39725694444</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45993.45324074074</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45993.58273148148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>44959.48167824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45988.49306712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45995</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45999.4191087963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45995</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45168.88072916667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45397.60945601852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>46000.43627314815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44386</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45166.65635416667</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46001.90539351852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45623.63510416666</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45194.49377314815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45222.56635416667</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45244</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45162.43773148148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45162.44449074074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45090.77837962963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>46007.70440972222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44679</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45128</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46008.51371527778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45611.70842592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>46010.49761574074</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46010.49818287037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>46010.52921296296</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45304</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46010.67133101852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45740.79685185185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44963</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44866.54954861111</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>46010.50359953703</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44529</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45686.59162037037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45686.60993055555</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45278.58283564815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>46019</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45111</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46019</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45245</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46029.47736111111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46029.48863425926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44678.43256944444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>44915.05086805556</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45797</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46031.40212962963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45104.61909722222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45796.48868055556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>46031.40054398148</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44824.31822916667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45304.56362268519</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45574.47497685185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45190</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>46035.30069444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45279.67762731481</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45753.32603009259</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44426.54175925926</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>44741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>44537.56209490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45236.44059027778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45236.44439814815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45317.65170138889</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46035.35650462963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45638.33574074074</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45764</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45803.50699074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46035.31605324074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45121</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45121</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45121</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46036.31258101852</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44950.47614583333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>46036.41478009259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45169</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45036</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>46036.43053240741</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46036.66730324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45665.64802083333</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45921.70836805556</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46041.39274305556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45749.4678587963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45805</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45763.61952546296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46043.61449074074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45048</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>46045.64295138889</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>46045.44012731482</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45447.41306712963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45463.64552083334</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46049.65488425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45230.68856481482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>46048</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45240.63111111111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45154</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46049</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45715.3468287037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45328</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45328</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46049.65270833333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>46049.66483796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46051.66256944444</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45769.35501157407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45632.4446875</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45194.39922453704</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44922</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45812.48452546296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>46057.57069444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45446.37311342593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45058</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46056.45358796296</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46057.56871527778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>46056.45521990741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46057.5653587963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45817.70034722222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45818</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45281.69575231482</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46056.46550925926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45769.6050462963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45274.6619212963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45686.61557870371</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45611.95675925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>46059.36828703704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>46059.40028935186</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46059.37333333334</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45594.49349537037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45594.49548611111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45820.65064814815</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45820.49263888889</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45820.64496527778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45818</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45825.38452546296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45825.69231481481</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45281.62967592593</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>46061.39715277778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45824.47944444444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45824.48297453704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45827</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45030</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45210</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45831.53054398148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45112</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44966.305</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45831.4883912037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45387.50104166667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45560.46328703704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45091</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45832.87528935185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45715</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44687.60125</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>46073.59329861111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45436.46103009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45260.3800462963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46073.71484953703</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>46072.43777777778</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45148.54725694445</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45148</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44545.65563657408</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45805</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45091.38644675926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45390.55701388889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45124.58091435185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45385</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46075.80827546296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46079.35677083334</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46079.3521412037</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46084.52283564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>46084.4408912037</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46083.35065972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45835.45113425926</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45342.75077546296</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45835.45200231481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45049.41876157407</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45835.37918981481</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46083.50642361111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45244.87707175926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45629.45599537037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46083</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>46083.63700231481</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46083.56542824074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45599.3781712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45840.44729166666</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45145</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>46087.45732638889</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45540</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>44845</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45169.45532407407</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44711.68930555556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45846</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45153</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45846</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44938</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45847.5616087963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44434</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45104.60564814815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45702.59452546296</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45769.48512731482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45387.36863425926</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45113</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>46097</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45579</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45513.4027199074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45215</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44532</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44427</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46099.48590277778</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46100.37087962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46100.34037037037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>46100.36679398148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>46099.45767361111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45224</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46100.63233796296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44641</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46100.34387731482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45390</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45853.69938657407</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45070.29650462963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45128</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45259</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45309.47016203704</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45309.48903935185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45488.29020833333</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45009</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46146.65170138889</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46146.65184027778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46146.65664351852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45686.33597222222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45103</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46147.6059837963</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46147.61996527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45253.58075231482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45250.30325231481</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46147.58696759259</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>46147.5946875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45016.62603009259</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45670</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>46147.5657175926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>46148.37179398148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45250.40770833333</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44397.68809027778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44986</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45740.59585648148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46108.42422453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46021</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>46021</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46021</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46021</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45183.5531712963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46021</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46021</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>46021</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46107.59799768519</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46107.60973379629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46108.49034722222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46149.67800925926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>44746</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>44977.63971064815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45114</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45114</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45296.33238425926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45181</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45090.5199537037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44867.6309375</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>46112.58732638889</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46112.59736111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45597.67458333333</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45401</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>44769.62064814815</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45685.42418981482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>44972.73002314815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>44769.61976851852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44928</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46112.41709490741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45568.34643518519</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>46153.60424768519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45061</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45267.31300925926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45384.34543981482</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>46113</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45097</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44904.33903935185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44904.34511574074</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45420.39990740741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45782.63381944445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>45504.53853009259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45583</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46161.45658564815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45753.32285879629</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>46162.59923611111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46162.60908564815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>45617.72848379629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44872</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45594.6340625</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>44370</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>46162.59502314815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>44670</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>45594.50951388889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45594.63260416667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45324</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45029.47953703703</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46161.63166666667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>46161.63422453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44651</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46162.61810185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45719.54616898148</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45719</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44393</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45533.45201388889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46119.9412037037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45147</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46163.49306712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>46163.50744212963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>46163.51511574074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45874.42462962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45392.39776620371</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45392</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>46163.49570601852</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45103</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45103</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45103.55109953704</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45350.33565972222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45247</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45559</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45579</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46163.49925925926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46163.50251157407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46163.51131944444</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45427</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45250.4330787037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45733.84600694444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46168.40664351852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45855.66106481481</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46125.55934027778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>46167.37201388889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>44552</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45180.44605324074</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45580.83032407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45883.58010416666</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44761</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45883.51181712963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45477.36865740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45190</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45559.33650462963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43953,7 +43953,7 @@
         <v>45153.31517361111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>46125.56210648148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>45421.62476851852</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45201</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>46168.40579861111</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>44424.56576388889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>44811.45271990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45113.57717592592</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46170.49400462963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45113</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46170.38807870371</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>44896</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46171.50009259259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45538</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>44903</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44502</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45754.66629629629</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>46170.49219907408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46171.30791666666</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46129.57209490741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46171.50685185185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45538.33878472223</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45301.65822916666</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44595</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45330</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45250.41039351852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45281</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>44592.5402662037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45722.67716435185</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45557.57826388889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45432.55671296296</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>44686.44046296296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45400.47762731482</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>44705.44402777778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45315.56436342592</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>45065</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44743</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45121</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>44831.38086805555</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46134.52199074074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>45302.71091435185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45573.91921296297</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>44676.47767361111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45881.56177083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45036.60653935185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45302.71799768518</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46134.55832175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45632.45528935185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46134.53310185186</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45188.47006944445</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45552.57313657407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45181</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45071</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45558.67806712963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45594.49958333333</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45594.51133101852</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45594.51443287037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>46134.49333333333</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45677</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45582.78583333334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45923.38232638889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45693.34945601852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45764.57550925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45939.49226851852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45644.54353009259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45056.48001157407</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45037.5341087963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45581.55803240741</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>44609</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>44652</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>44956.39506944444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45300.55637731482</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45211.82909722222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>44468</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45894.43885416666</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45923.58896990741</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45210.6784837963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45883.6346412037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45883.64103009259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45827.56438657407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45533.38872685185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>44986</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45638.51944444444</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45743</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45687.94340277778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45327</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>44741.5471412037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45338.5585300926</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45791.48850694444</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44960.58287037037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>44843.29655092592</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45670</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45665.6562962963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45833.66576388889</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45782.64549768518</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>44874</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>44874.58840277778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45688.62399305555</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45909</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>44963</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45775.45998842592</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44600</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>45412.44925925926</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45412.45357638889</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45757.4737037037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45316</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45316.41688657407</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45551</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45835.3862962963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>44896</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45601.46222222222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45679.92653935185</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45316.42096064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45841.85952546296</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46139.65122685185</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45826</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45960.38902777778</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45140.49438657407</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45426</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45446</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45392.38908564814</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45166.48473379629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45905.32910879629</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45345.30666666666</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44915.74278935185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44972</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45463</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>44998</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45846</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45698.61065972222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45468.46099537037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>45827.5565162037</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45874</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45818</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>44880.29931712963</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51765,7 +51765,7 @@
         <v>45676.75392361111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45810.66587962963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45127.38489583333</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45127</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45288.37354166667</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45022.55644675926</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>44869.55530092592</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>44998.41530092592</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>44522</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45217.47178240741</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>46183.44533564815</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>46183.48128472222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45085.48240740741</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>44609</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>44457.86240740741</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45329</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45686.5972800926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45722.95646990741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45560.44628472222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>44577.67608796297</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45419.61466435185</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>44831</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45611.70576388889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45679.49554398148</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45679.60159722222</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45030</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45300.54975694444</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45877.47127314815</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>44774.52144675926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45128.63200231481</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45128</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45111.55594907407</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45638.33728009259</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>46183.00041666667</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45386.86943287037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45165.53953703704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45533.63113425926</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>46183.55180555556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45555.60236111111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45141.33791666666</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45141</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>46183.54673611111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>44496</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45579.46674768518</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45754</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45754.568125</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45012.4278587963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45127</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44867.62049768519</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45552.70320601852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45247</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45511.58850694444</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>44922.87642361111</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45048</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45205</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>44501</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>44995</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>44876.69168981481</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45495.89736111111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>44963.87038194444</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45106.5721875</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45385.58976851852</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>45385.59068287037</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>44900.54149305556</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>44473</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55552,7 +55552,7 @@
         <v>45199</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45070.29798611111</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>44494.60379629629</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>45754</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45224.33578703704</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55894,7 +55894,7 @@
         <v>44711.39636574074</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>44782</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45572</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>45204</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45443.55731481482</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56184,7 +56184,7 @@
         <v>45726.34802083333</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>45139.7190625</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>45373.49592592593</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56355,7 +56355,7 @@
         <v>44452.39638888889</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56412,7 +56412,7 @@
         <v>45369.61829861111</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56469,7 +56469,7 @@
         <v>45127.60962962963</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45127.61971064815</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45372</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56640,7 +56640,7 @@
         <v>45219</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         <v>45594.50804398148</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45594.5128587963</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>44690.40230324074</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45385</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>45702.65407407407</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>45000</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45446.40025462963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>44858</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45594.49064814814</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45594.49494212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45594.49597222222</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45594.49865740741</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45594.51395833334</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45594.51512731481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45302.78386574074</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45302.78486111111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>44959.48619212963</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>44894</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45267.60236111111</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45198</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44651</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45280</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>45509</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58053,7 +58053,7 @@
         <v>45369.66939814815</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>45447.35372685185</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>45378</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45495.70517361111</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58281,7 +58281,7 @@
         <v>45446.39304398148</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>45008.52043981481</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>44739.6016087963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45519.33865740741</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58509,7 +58509,7 @@
         <v>45176.58175925926</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58566,7 +58566,7 @@
         <v>45176.58371527777</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>45644.62018518519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>44812</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>44992</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>45139.69394675926</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58851,7 +58851,7 @@
         <v>45244</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>44384</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         <v>45232.63908564814</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>45705</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45078</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45737.55483796296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45108</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>44749</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45468.49049768518</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45127.43435185185</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45273</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45392.39731481481</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45608.43087962963</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>44894</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>44677.39790509259</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45763</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>45089.44758101852</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59840,7 +59840,7 @@
         <v>45236.6053587963</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
         <v>45392.39274305556</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59959,7 +59959,7 @@
         <v>45342.53827546296</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45189.70568287037</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45189.71008101852</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>44909.65577546296</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45190.38162037037</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45714.9666087963</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>44599.52814814815</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45614.61105324074</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>45692</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45384.80710648148</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45448.38922453704</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45294</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>45587</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>45219.45643518519</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>45147</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>44536.55450231482</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>44732</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45216.70546296296</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45198.33086805556</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44379.55199074074</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45644.57841435185</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45014</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61223,7 +61223,7 @@
         <v>44897</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45447.41501157408</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45649.6471875</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45014.55976851852</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>45743</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -566,7 +566,7 @@
         <v>45468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>45888</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45127</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45384</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45812</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>46175</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>46188</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46188</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45081</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45490</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45294</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45995</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45356</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44445</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45190</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45649</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45883</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45093</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45545</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44532</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45554</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>46147</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45687</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45587</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>46161</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45874</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44721</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44645</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44386</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44490</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45544</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>44872</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45688</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45098</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45533</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45279</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45594</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45594</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45754</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45392</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44673</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45280</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45643</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45912</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45617</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45606</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46182</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45964</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45428</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45978</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45273</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45280</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46045</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44746</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44741</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>46161</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>46161</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45594</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45327</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45824</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44693</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44812</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>44458</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>44518</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44536</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44438</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44764</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44434</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44519</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44463</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44501</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44814</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44438</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44446</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44393</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44643</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44515</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44814</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44480</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44525</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44516</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44466</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44803</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44470</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44400</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44691</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44739</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44590</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44820</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44814</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44704</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44442</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44769</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44820</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44711</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44474</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44508</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44880</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44495</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44515</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44599</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44376</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44416</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44495</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44476</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44599</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44876</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44671</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44466</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44496</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>44397</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44396</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44750</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44379</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44568</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44420</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44427</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44442</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>44426</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44470</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44606</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44613</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44474</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44420</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44412</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44610</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44610</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44491</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44740</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44483</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>44617</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44426</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44457</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44726</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44468</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44551</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>44393</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44599</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44463</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44367</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44781</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44494</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44522</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>44532</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44532</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44498</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44439</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44860</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44596</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44571</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44998</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44592</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44537</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45103</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44489</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44573</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44487</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44712</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45058</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44603</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44896</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45315</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45315</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44596</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44579</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44424</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44711</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44979</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44438</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44406</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45386</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45359</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45190</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44769</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44959</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45573</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45594</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45594</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45594</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>44867</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45230</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44599</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44473</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44843</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44894</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45672</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44560</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44896</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45245</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44474</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44820</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44820</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45559</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44532</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44502</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45597</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45219</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44812</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45061</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45572</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45304</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44452</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45390</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44427</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45412</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45194</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44595</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45029</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44992</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45552</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45199</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45219</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44903</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44938</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44814</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44814</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45181</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45147</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44489</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>44489</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45014</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45105</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45715</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>44501</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45557</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45412</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45324</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45140</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45552</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44483</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45378</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45534</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45560</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45369</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44599</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44869</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45554</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>44508</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>44761</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45338</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45244</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45517</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45754</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45754</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45408</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45468</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45057</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45169</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44434</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45427</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45583</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45392</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45400</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45594</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44670</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45446</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44977</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45372</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44537</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45009</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45679</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44732</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45176</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44956</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45281</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44537</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44711</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45071</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45583</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45161</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45288</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45219</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45757</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45090</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45384</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44379</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45229</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45345</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45019</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45222</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44487</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45579</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45611</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45280</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44970</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44880</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45884</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45676</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45162</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44874</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45201</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45281</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45392</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45581</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45504</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44502</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45049</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44896</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44894</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45622</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45240</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45665</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45883</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45300</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45763</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45762</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45302</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45764</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45225</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45679</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45127</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44393</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45189</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45189</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45302</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45722</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45617</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45386</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45463</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45769</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45392</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>45392</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45446</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>44960</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45594</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45594</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45594</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45594</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45594</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45594</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45594</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45594</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45586</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44687</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44986</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45211</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45632</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45281</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45432</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45232</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45180</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45714</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45670</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45250</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45139</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45317</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45236</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45112</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45373</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45448</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45629</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45328</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44494</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45477</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45022</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45693</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45555</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45638</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45754</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45309</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45309</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45446</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45463</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45611</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>44904</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44904</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44384</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44711</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45468</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45127</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45127</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45551</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44573</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45224</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>44972</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>44972</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45519</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45108</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45702</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44854</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45169</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45244</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>44894</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45608</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45205</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45070</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44967</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44900</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44900</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45012</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45154</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>44981</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45145</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44547</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45294</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44532</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45166</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44998</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45181</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45342</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45330</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44950</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45385</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45385</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45495</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45103</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45103</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45103</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>44929</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45558</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45538</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45114</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45114</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44545</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44656</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44739</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45443</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45147</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45217</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44831</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45128</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45194</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45488</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45219</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45124</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45280</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45568</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>44880</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44774</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45692</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45705</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44922</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45894</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45890</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45033</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45541</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45856</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45895</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45645</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45719</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45121</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44782</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45016</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45902</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45902</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45902</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45645</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45127</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45835</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45168</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45061</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45582</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45905</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45905</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45560</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45460</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44995</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45113</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45113</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44536</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44909</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45910</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44986</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45686</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45737</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45909</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45224</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45894</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45304</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45244</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>44427</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45692</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45787</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45250</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45911</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>44397</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45714</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>44858</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44502</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45091</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45030</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45557</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45579</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45533</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45579</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45702</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45216</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45165</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45918</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45397</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45918</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45918</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45918</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45918</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45918</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45918</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45194</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45547</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45691</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44522</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45777</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45519</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45777</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45715</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45777</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45048</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45780</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45780</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45924</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45190</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45782</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45780</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45784</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45546</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44991</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45513</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45783</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45925</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45534</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45478</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45642</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44781</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45210</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45608</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45108</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44909</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45716</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44922</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45753</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45614</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44552</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44894</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45250</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45141</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45614</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45719</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45719</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45533</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44529</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45716</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44641</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45933</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>46183</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>45789</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45937</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45937</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45937</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44874</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45715</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45714</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45267</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45791</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44894</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45896</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45036</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46183</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45796</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45599</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44523</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45233</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>44600</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44457</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45632</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44473</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45153</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44713</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45797</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45946</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44897</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46183</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45764</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45204</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45737</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>46183</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45574</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45950</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45665</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44824</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45557</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44928</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46183</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45279</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45749</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45952</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45923</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45329</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45273</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44577</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45436</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45106</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45805</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45090</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45763</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45561</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45447</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45392</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45447</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45211</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45104</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45078</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45726</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>45946</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45341</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45127</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45953</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45538</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45128</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45128</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
         <v>45350</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45387</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45812</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45924</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45240</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45964</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45121</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45121</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45121</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45387</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44959</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45818</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45769</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45820</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45820</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45820</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45030</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>46188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45971</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45166</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45824</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45824</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45825</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45446</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45825</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45973</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45392</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45324</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45827</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>45831</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45973</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45975</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45558</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45309</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45831</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45309</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45805</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>45975</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45832</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45979</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45979</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45835</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45835</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45980</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45835</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>44988</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45127</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46146</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>46146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45840</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45540</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46188</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45846</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45846</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45638</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45685</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45611</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>44866</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45847</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>46146</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>46188</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45139</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45390</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45112</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45853</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45580</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45740</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45014</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45993</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45993</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45316</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45988</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45384</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>45995</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45097</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46189</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45330</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45267</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45219</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45999</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45782</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45330</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45644</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>46147</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>46147</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46148</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45198</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45008</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46000</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45000</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44609</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45733</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45722</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45036</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>46190</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>46001</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45065</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45874</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45028</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45594</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45594</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45594</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45594</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45594</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45509</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46008</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45644</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>45594</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45594</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45594</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>46007</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45601</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46147</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>46147</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45855</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45316</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46010</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46010</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>46010</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45316</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45056</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46010</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>46010</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45623</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44858</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45517</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45372</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45397</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>45686</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46147</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44764</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45278</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>45091</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45579</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45385</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45385</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>46019</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45440</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45679</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45215</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>44876</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>46029</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45495</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>46021</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>46021</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45210</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45754</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>46029</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>46031</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         <v>45244</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>44679</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>44678</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>46191</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45775</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>46191</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>46031</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>46021</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>46021</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>46021</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>44705</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44802</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>46191</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>45420</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50620,7 +50620,7 @@
         <v>45140</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>46036</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46035</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>46035</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45921</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50972,7 +50972,7 @@
         <v>45686</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51029,7 +51029,7 @@
         <v>45686</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>46036</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>46036</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>46035</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>46036</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>45085</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51376,7 +51376,7 @@
         <v>46191</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44676</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>44620</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46149</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>46021</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46021</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45253</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45247</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46041</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45631</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>44676</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>45236</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52127,7 +52127,7 @@
         <v>45114</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>45679</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>44690</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>46043</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>44705</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>44651</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>45460</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>46048</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>46045</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45421</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46045</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45176</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>45250</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44746</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>46049</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45753</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>46049</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>46049</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>46049</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>45288</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>46051</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44686</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46056</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45260</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>44915</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>46056</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>46056</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>44651</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>46057</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46057</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>46057</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>44831</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>46059</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>46061</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45301</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45247</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45309</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45121</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>46059</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>46059</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44677</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>44811</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>44749</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45104</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>44452</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45769</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>44496</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>44858</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>45274</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>45740</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45246</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46072</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>45743</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>46073</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         <v>45198</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>45644</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45128</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55490,7 +55490,7 @@
         <v>46073</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46075</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45686</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45278</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>45559</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45181</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>45141</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>45194</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>45302</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>46079</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45726</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45401</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>44370</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46079</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45152</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>46083</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46083</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46083</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45702</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>46083</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>46083</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46084</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>46084</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45541</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45300</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45300</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>46087</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45342</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45302</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45322</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45511</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>44915</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44652</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>44434</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>44537</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>44609</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>45183</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46097</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45121</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>45420</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>45253</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>44386</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>44845</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>46099</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>44426</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>44915</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>44552</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45070</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>46099</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>46100</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>46100</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46100</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>46100</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>46100</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46107</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>44769</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>44769</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>46153</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>46108</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>46108</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>46113</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46112</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>46112</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>46112</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59205,7 +59205,7 @@
         <v>46161</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46163</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45594</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59381,7 +59381,7 @@
         <v>46119</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>46163</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59495,7 +59495,7 @@
         <v>45594</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>46162</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46162</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46163</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>46163</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>46162</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>46162</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>46163</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>46163</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>46163</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46125</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>46167</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>46125</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>46168</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60298,7 +60298,7 @@
         <v>46168</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>46170</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>46170</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46171</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60526,7 +60526,7 @@
         <v>46171</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46171</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46170</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>46129</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>46134</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60811,7 +60811,7 @@
         <v>46134</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60868,7 +60868,7 @@
         <v>46134</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60925,7 +60925,7 @@
         <v>46134</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>45881</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>45638</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45677</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45835</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45743</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61267,7 +61267,7 @@
         <v>45827</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>45698</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45810</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45826</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45670</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>45905</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>45923</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>45833</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61733,7 +61733,7 @@
         <v>45883</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>45883</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45775</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>45846</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61961,7 +61961,7 @@
         <v>45782</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45923</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62075,7 +62075,7 @@
         <v>45426</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62132,7 +62132,7 @@
         <v>45939</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>45827</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>45841</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>45686</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>44468</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45877</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45818</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
         <v>45791</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>45419</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45960</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46139</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45909</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -566,7 +566,7 @@
         <v>45468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>45888</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45127</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45384</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45812</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>46175</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>46188</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>46188</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45081</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45490</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45294</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45995</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45356</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44445</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45190</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45649</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45883</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45093</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45545</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44532</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45554</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>46147</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45687</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45587</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>46161</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45874</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44721</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44645</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44386</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44490</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45544</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>44872</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45688</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45098</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45533</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45279</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45594</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45594</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45754</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45392</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44673</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45280</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45643</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45912</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45617</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45606</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46182</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45964</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45428</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45978</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45273</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45280</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46045</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44746</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44741</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>46161</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>46161</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45594</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45327</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45824</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44693</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44812</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>44458</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>44518</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44536</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44438</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44764</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44434</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44519</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44463</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44501</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44814</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44438</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44446</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44393</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44643</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44515</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44814</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44480</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44525</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44516</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44466</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44803</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44470</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44400</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44691</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44739</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44590</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44820</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44814</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44704</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44442</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44769</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44820</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44711</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44474</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44508</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44880</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44495</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44515</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44599</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44376</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44416</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44495</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44476</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44599</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44876</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44671</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44466</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44496</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>44397</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44396</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44750</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44379</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44568</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44420</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44427</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44442</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>44426</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44470</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44606</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44613</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44474</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44420</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44412</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44610</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44610</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44491</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44740</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44483</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>44617</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44426</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44457</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44726</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44468</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44551</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>44393</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44599</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44463</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44367</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44781</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44494</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44522</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>44532</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44532</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44498</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44439</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44860</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44596</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44571</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44998</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44592</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44537</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45103</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44489</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44573</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44487</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44712</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45058</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44603</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44896</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45315</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45315</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44596</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44579</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44424</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44711</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44979</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44438</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44406</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45386</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45359</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45190</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44769</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44959</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45573</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45594</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45594</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45594</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>44867</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45230</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44599</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44473</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44843</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44894</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45672</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44560</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44896</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45245</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44474</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44820</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44820</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45559</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44532</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44502</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45597</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45219</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44812</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45061</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45572</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45304</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44452</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45390</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44427</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45412</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45194</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44595</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45029</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44992</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45552</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45199</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45219</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44903</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44938</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44814</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44814</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45181</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45147</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44489</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>44489</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45014</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45105</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45715</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>44501</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45557</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45412</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45324</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45140</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45552</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44483</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45378</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45534</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45560</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45369</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44599</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44869</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45554</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>44508</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>44761</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45338</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45244</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45517</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45754</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45754</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45408</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45468</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45057</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45169</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44434</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45427</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45583</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45392</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45400</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45594</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44670</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45446</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44977</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45372</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44537</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44574</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45009</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45679</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44602</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44732</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45176</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44956</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45281</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44537</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44711</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45071</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45583</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45161</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45288</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45219</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45757</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45090</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45384</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44379</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45229</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45345</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45019</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45222</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44487</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45579</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45611</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45280</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44970</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44880</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45884</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45676</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45162</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44874</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45201</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45281</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45392</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45581</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45504</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44502</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45049</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44896</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44894</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45622</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45240</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45665</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45883</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45300</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45763</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45762</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45302</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45764</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45225</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45679</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45127</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44393</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45189</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45189</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45302</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45722</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45617</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45386</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45463</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45769</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45392</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>45392</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45446</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>44960</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45594</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45594</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45594</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45594</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45594</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45594</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45594</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45594</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45586</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44687</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44986</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45211</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45632</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45281</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45432</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45232</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45180</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45714</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45670</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45250</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45139</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45317</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45236</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45112</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45373</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45448</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45629</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45328</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44494</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45477</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45022</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45693</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45555</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45638</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45754</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45309</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45309</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45446</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45463</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45611</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>44904</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44904</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44384</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44711</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45468</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45127</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45127</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45551</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44573</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45224</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44966</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>44972</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>44972</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45519</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45108</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45702</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44854</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45169</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45244</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>44894</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45608</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45205</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45070</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44967</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44900</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44900</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45012</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45154</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>44981</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45145</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44547</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45294</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44532</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45166</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44998</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45181</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45342</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45330</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44950</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45385</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45385</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45495</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45103</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45103</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45103</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>44929</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45558</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45538</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45114</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45114</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44545</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44656</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44739</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45443</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45147</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45217</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44831</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45128</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45194</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45488</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45219</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45124</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45280</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45568</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>44880</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44774</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45692</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45705</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44922</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45894</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45890</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45033</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45541</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45856</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45895</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45645</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45719</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45121</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44782</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45016</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45902</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45902</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45902</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45645</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45127</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45835</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45168</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45061</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45582</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45905</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45905</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45560</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45460</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44995</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45113</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45113</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44536</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44909</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45910</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44986</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45686</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45737</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45909</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45224</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45894</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45304</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45244</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>44427</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45692</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45787</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45250</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45911</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>44397</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45714</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>44858</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44502</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45091</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45030</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45557</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45579</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45533</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45579</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45702</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45216</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45165</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45918</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45397</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45918</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45918</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45918</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45918</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45918</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45918</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45194</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45547</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45691</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44522</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45777</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45519</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45777</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45715</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45777</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45048</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45780</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45780</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45924</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45190</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45782</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45780</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45784</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45546</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44991</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45513</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45783</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45925</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45534</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45478</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45642</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44781</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45210</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45608</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45108</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44909</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45716</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44922</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45753</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45614</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44552</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44894</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45250</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45141</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45614</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45719</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45719</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45533</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44529</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45716</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44641</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45933</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>46183</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>45789</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45937</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45937</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45937</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44874</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45715</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45714</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45267</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45791</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44894</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45896</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45036</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46183</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45796</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45599</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44523</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45233</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>44600</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44457</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45632</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44473</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45153</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44713</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45797</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45946</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44897</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46183</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45764</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45204</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45737</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>46183</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45574</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45950</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45665</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44824</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45557</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44928</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46183</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45279</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45749</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45952</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45923</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45329</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45273</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44577</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45436</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45106</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45805</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45090</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45763</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45561</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45447</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45392</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45447</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45211</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45104</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45078</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45726</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>45946</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45341</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45127</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45953</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45538</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45128</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45128</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
         <v>45350</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45387</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45812</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45924</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45240</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45964</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45121</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45121</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45121</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45387</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44959</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45818</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45769</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45820</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45820</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45820</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45030</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>46188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45971</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45166</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45824</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45824</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45825</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45446</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45825</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45973</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45392</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45324</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45827</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>45831</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45973</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45975</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45558</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45309</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45831</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45309</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45805</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>45975</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45832</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45979</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45979</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45835</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45835</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45980</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45835</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>44988</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45127</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46146</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>46146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45840</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45540</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46188</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45846</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45846</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45638</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45685</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45611</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>44866</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45847</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>46146</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>46188</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45139</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45390</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45112</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45853</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45580</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45740</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45014</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45993</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45993</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45316</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45988</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45384</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>45995</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45097</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46189</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45330</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45267</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45219</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45999</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45782</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45330</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45644</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>46147</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>46147</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46148</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45198</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45008</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46000</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45000</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44609</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45733</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45722</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45036</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>46190</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>46001</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45065</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45874</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45028</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45594</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45594</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45594</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45594</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45594</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45509</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46008</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45644</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>45594</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45594</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45594</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>46007</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45601</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46147</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>46147</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45855</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45316</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46010</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46010</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>46010</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45316</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45056</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46010</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>46010</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45623</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44858</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45517</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45372</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45397</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>45686</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46147</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44764</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45278</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>45091</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45579</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45385</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45385</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>46019</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46019</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45440</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45679</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45215</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>44876</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>46029</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45495</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>46021</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>46021</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45210</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45754</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>46029</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>46031</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         <v>45244</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>44679</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>44678</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>46191</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45775</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>46191</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>46031</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>46021</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>46021</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>46021</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>44705</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44802</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>46191</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>45420</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50620,7 +50620,7 @@
         <v>45140</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>46036</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46035</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>46035</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45921</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50972,7 +50972,7 @@
         <v>45686</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51029,7 +51029,7 @@
         <v>45686</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>46036</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>46036</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>46035</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>46036</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>45085</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51376,7 +51376,7 @@
         <v>46191</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44676</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>44620</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46149</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>46021</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46021</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45253</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45247</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46041</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45631</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>44676</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>45236</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52127,7 +52127,7 @@
         <v>45114</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>45679</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>44690</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>46043</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>44705</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>44651</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>45460</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>46048</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>46045</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45421</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46045</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45176</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45121</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>45250</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44746</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>46049</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45753</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>46049</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>46049</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>46049</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>45288</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>46051</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44686</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46056</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45260</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>44915</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>46056</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>46056</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>44651</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>46057</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46057</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>46057</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>44831</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>46059</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>46061</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45301</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45247</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45309</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45121</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>46059</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>46059</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44677</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>44811</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>44749</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45104</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>44452</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45769</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>44496</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>44858</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>45274</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>45740</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45246</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46072</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>45743</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>46073</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         <v>45198</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>45644</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45128</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55490,7 +55490,7 @@
         <v>46073</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>46075</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45686</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45278</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>45559</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45181</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>45141</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>45194</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>45302</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>46079</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45726</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45401</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>44370</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46079</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45152</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>46083</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46083</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46083</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45702</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>46083</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>46083</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46084</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>46084</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45541</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45300</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45300</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>46087</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45342</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45302</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45322</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45511</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>44915</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44652</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>44434</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>44537</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>44609</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>45183</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46097</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45121</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>45420</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>45253</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>44386</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>44845</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>46099</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>44426</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>44915</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>44552</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45070</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>46099</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>46100</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>46100</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>46100</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>46100</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>46100</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46107</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>44769</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>44769</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>46153</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>46108</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>46108</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>46113</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46112</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>46112</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>46112</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59205,7 +59205,7 @@
         <v>46161</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46163</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45594</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59381,7 +59381,7 @@
         <v>46119</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>46163</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59495,7 +59495,7 @@
         <v>45594</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>46162</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46162</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46163</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>46163</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>46162</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>46162</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>46163</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>46163</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>46163</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>46125</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>46167</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>46125</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>46168</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60298,7 +60298,7 @@
         <v>46168</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>46170</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>46170</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46171</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60526,7 +60526,7 @@
         <v>46171</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46171</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46170</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>46129</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>46134</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60811,7 +60811,7 @@
         <v>46134</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60868,7 +60868,7 @@
         <v>46134</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60925,7 +60925,7 @@
         <v>46134</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>45881</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>45638</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45677</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45835</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45743</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61267,7 +61267,7 @@
         <v>45827</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>45698</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45810</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45826</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45670</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>45905</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>45923</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>45833</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61733,7 +61733,7 @@
         <v>45883</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>45883</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45775</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>45846</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61961,7 +61961,7 @@
         <v>45782</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45923</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62075,7 +62075,7 @@
         <v>45426</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62132,7 +62132,7 @@
         <v>45939</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>45827</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>45841</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>45686</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>44468</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45877</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45818</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
         <v>45791</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>45419</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45960</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46139</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45909</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -566,7 +566,7 @@
         <v>45384</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>45468</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45127</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45888</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46175</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>46188</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46188</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44958</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45081</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45490</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45294</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45995</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45356</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>44445</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>44532</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45687</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45093</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45587</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45190</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45447</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45649</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45554</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45545</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45883</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>46161</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45874</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>46147</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44721</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44645</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>44490</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45594</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45594</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45279</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45392</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45280</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45688</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45428</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44386</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>45643</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44746</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45273</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44741</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44872</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45533</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45544</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45754</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45098</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44673</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45280</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45369</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45964</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45978</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45617</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45606</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>46045</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45594</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>46161</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46161</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45327</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45824</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>46182</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44693</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44812</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44458</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44518</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44536</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44438</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44764</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44434</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44519</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44463</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44501</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44814</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44438</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44393</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44643</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44814</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44525</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44480</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44578</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44516</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44803</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44470</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44466</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44400</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44691</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44739</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44590</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44820</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44814</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44442</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44769</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44820</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44711</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44880</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44495</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44508</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44740</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44483</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44442</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44457</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44617</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44426</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44416</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44476</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44515</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44543</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44726</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44426</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44606</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44599</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44599</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44470</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44389</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44551</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44651</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44876</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44393</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44671</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44613</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44474</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>44746</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44466</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44376</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44412</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44496</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>44420</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44397</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44396</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44463</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>44750</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44610</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44494</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44379</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44568</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44420</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44704</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44781</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44522</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44532</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44532</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44579</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44610</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44711</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44498</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44439</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44491</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44438</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44489</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44489</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44769</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44860</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44596</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44427</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44483</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44573</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44502</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44812</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44712</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44508</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44452</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44427</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44603</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44820</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44820</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44434</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44596</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44537</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44574</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44537</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45386</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45420</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44571</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44802</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44573</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45477</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44489</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44967</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45324</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44487</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44894</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44915</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44523</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44595</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45330</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45594</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45594</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45594</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45594</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45250</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45594</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45048</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45715</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45236</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44592</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44406</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45460</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44502</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45463</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45722</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45672</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44537</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44764</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45230</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45594</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45594</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45554</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45557</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>45240</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45154</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45762</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45558</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45057</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45715</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45328</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45328</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45432</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45775</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44686</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45056</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45769</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45679</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>44988</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45152</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45330</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44991</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44900</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45322</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44656</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44970</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45181</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45397</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44713</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44532</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45632</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44908</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45033</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44602</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45194</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44922</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45446</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45400</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45058</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>44705</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45315</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44620</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45065</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44743</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45121</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44831</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45281</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45561</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44894</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45274</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45686</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45611</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45541</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45541</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44599</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45302</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45573</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45341</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44676</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45594</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45594</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45726</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45036</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45219</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45281</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45392</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45302</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45315</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45114</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45359</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45555</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45030</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45632</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45330</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45210</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45714</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45188</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45112</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44966</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45105</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45387</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45560</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45552</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45091</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45181</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45579</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45557</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44741</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45715</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>44687</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45691</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44473</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45071</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45557</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45558</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45594</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45583</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45408</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45594</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45594</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45586</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45309</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44854</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45436</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45260</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45211</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44560</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44545</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45737</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45091</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45693</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45176</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45176</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45764</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45390</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45124</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44909</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45644</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45385</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44812</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>44992</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45686</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45233</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45309</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45139</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45644</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45056</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44705</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45253</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44552</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45309</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45244</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45581</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44609</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44652</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44956</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45300</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45300</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45342</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>44858</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44814</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44814</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45061</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45049</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45244</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45629</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45599</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45280</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45145</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45412</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45210</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44845</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44929</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45372</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45533</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45169</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44711</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44746</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>44986</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>44896</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45153</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44938</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44741</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44981</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45338</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44960</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45019</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44843</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44434</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45194</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45104</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45702</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45769</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45387</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45714</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45246</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45140</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45665</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45112</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44874</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>44874</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45244</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45219</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44384</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>44959</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45232</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45113</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45705</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45579</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45078</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45168</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45513</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45737</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45108</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45215</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44532</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44427</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44600</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45412</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45412</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44386</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45166</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45757</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45316</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45316</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45623</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45551</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45224</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45194</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>44641</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>44896</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45222</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45244</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45601</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45070</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45162</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45162</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45090</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44679</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45128</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45128</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45611</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45309</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45309</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45679</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45009</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45304</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45316</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45686</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44866</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45103</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45140</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44858</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45253</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45446</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45392</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45250</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44529</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45016</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45686</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45686</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45670</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45278</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45166</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45250</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44397</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44986</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45245</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45345</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44915</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44972</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44749</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45468</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45127</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44678</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>44915</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45463</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44998</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45183</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45104</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44977</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45304</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45190</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45114</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45114</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45181</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45090</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44867</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45279</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45597</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45753</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45273</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45468</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44880</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45676</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45127</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45288</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45022</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>44869</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44426</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45401</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45236</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45236</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45317</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45392</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45685</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45608</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44894</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45638</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45121</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45121</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45121</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44950</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45169</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44928</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45036</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45568</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44998</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45061</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45217</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44677</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45763</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45089</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45236</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45085</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45392</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44609</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>44904</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>44904</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>44457</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45342</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45189</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45189</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44909</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45190</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45714</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44599</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45812</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45614</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45420</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45722</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45560</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45692</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45384</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45504</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45817</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45818</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45611</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45679</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45583</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45769</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45679</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45753</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45030</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45448</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45294</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45820</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45617</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45820</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45818</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45300</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45825</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45825</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45324</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45029</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45824</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44651</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44774</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45219</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45128</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45128</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45147</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45111</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44536</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45719</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44393</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45533</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45827</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45638</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44732</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45147</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45386</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45216</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45831</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45392</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45165</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45392</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45831</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45103</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45103</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45103</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45350</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45832</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45141</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45141</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45247</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45559</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45579</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45805</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45835</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45427</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45250</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45835</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45733</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45835</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45198</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44496</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44552</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45579</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45180</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45580</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>44761</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45840</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45477</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45559</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45540</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45153</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45754</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45421</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44424</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45754</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44811</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>45113</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45113</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45847</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44379</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45390</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>45853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45012</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>45644</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44896</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45014</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44897</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45127</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45740</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45538</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44903</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44502</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45014</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45743</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44867</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45267</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45538</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45384</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45301</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45552</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45247</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45782</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45534</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45702</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>45219</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44676</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45511</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45121</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45121</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45121</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45440</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44922</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45048</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45645</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45874</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45205</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45281</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45692</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45028</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45777</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45777</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45194</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44501</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>45855</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44995</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44876</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45547</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45777</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45161</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45240</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45495</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>44963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45106</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45780</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45780</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45385</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45385</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45754</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>44900</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44473</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45199</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45622</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45288</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45229</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45478</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45278</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>45546</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45783</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45782</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>45780</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45883</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45201</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>44494</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>45280</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45225</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45127</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45534</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45933</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44894</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45108</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44880</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44781</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45754</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45224</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45161</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45937</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>44711</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44782</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45572</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45937</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44487</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45896</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>45889</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45642</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>44547</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45816</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45890</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45895</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45894</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45443</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45726</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45139</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45856</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45373</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45897</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45614</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44452</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45716</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45608</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>45946</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45950</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45369</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45923</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45127</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45127</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45902</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45372</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45219</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45810</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45594</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45594</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>44690</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45952</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45719</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45645</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45835</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45902</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45902</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45905</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45905</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45385</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45909</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45702</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45000</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45446</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>44858</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45594</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45594</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45594</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45594</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45594</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45594</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45302</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45302</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45911</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>44959</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45910</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45787</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45958</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>44894</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45267</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45716</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45791</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45198</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>44651</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45946</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>45953</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>45540</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45509</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45916</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>45964</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45447</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45918</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45918</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45924</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45918</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>45918</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45918</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45918</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45378</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45918</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45495</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45446</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45008</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>44739</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45924</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45971</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45925</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45924</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45924</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45973</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45973</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45797</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>45796</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45979</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44824</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45979</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45980</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45574</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45764</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45803</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45993</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45993</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45665</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45988</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45749</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45995</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45805</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45999</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45763</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>46000</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>46001</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46007</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>46008</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>46010</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>46010</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46010</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46010</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46010</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>46019</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52328,7 +52328,7 @@
         <v>46019</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>46029</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46029</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46031</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46031</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>46035</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46035</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>46035</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>46036</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>46036</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52923,7 +52923,7 @@
         <v>46036</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52980,7 +52980,7 @@
         <v>46036</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>45921</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46041</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>46043</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>46045</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>46045</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46049</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53379,7 +53379,7 @@
         <v>46048</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>46049</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46049</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>46049</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>46051</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>46057</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>46056</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>46057</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>46056</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>46057</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>46056</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>46059</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54063,7 +54063,7 @@
         <v>46059</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>46059</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46061</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>46073</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46073</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>46072</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>46075</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54462,7 +54462,7 @@
         <v>46079</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>46079</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>46084</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46084</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54690,7 +54690,7 @@
         <v>46083</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>46083</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>46083</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>46083</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46083</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>46087</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>46097</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>46100</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46100</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55260,7 +55260,7 @@
         <v>46100</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>46099</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>46100</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46100</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46108</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>46107</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46108</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46112</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>46112</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>44769</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>44769</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>46112</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55954,7 +55954,7 @@
         <v>46113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>46161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>46162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56125,7 +56125,7 @@
         <v>46162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45594</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>46162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>45594</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56363,7 +56363,7 @@
         <v>46162</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56420,7 +56420,7 @@
         <v>46119</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56534,7 +56534,7 @@
         <v>46163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56591,7 +56591,7 @@
         <v>46163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>46163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46163</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>46163</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46163</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46168</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>46167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46125</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>46168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>46170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>46170</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>46171</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>46129</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46171</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57503,7 +57503,7 @@
         <v>46134</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>45881</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57617,7 +57617,7 @@
         <v>46134</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>46134</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46134</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>45677</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>45582</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45923</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45939</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>44468</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>45894</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45923</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45883</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45883</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45827</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45638</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45743</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45791</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45670</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45833</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45782</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45909</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45775</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45835</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45841</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>46139</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58985,7 +58985,7 @@
         <v>45826</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45960</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>45426</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45905</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45846</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45698</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59332,7 +59332,7 @@
         <v>45827</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45818</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45810</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>44522</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46183</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59622,7 +59622,7 @@
         <v>46183</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45686</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>44577</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45419</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59907,7 +59907,7 @@
         <v>45877</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46183</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60021,7 +60021,7 @@
         <v>46183</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>46183</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46188</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>46189</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>46146</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>46146</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46146</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>46147</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>46147</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>46147</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46147</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46147</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>46021</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>46191</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46149</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>46191</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>46191</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>46190</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>46021</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46021</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45397</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>46021</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46021</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61332,7 +61332,7 @@
         <v>46191</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46191</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>46148</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>46021</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>46021</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>46153</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61674,7 +61674,7 @@
         <v>46195</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>46188</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>45995</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45789</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45517</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45631</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>46198</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46198</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46198</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>46199</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46198</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46188</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62358,7 +62358,7 @@
         <v>46199</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -566,7 +566,7 @@
         <v>45384</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>45468</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45127</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>45812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45888</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46175</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>46188</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46188</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44958</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45081</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45490</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45294</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45995</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45356</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>44445</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>44532</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45687</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45093</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45587</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45190</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45447</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45649</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45554</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45545</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45883</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>46161</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45874</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>46147</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44721</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44645</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>44490</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45594</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45594</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45279</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45392</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45280</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45688</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45428</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44386</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>45643</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44746</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45273</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44741</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44872</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45533</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45544</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45754</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45098</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44673</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45280</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45369</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45964</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45978</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45617</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45606</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>46045</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45594</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>46161</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46161</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45327</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45824</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>46182</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44693</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44812</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44458</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44518</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44536</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44438</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44764</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44434</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44519</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44463</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44501</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44814</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44438</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44393</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44643</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44814</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44525</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44480</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44578</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44516</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44803</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44470</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44466</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44400</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44691</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44739</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44590</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44820</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44814</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44442</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44769</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44820</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44711</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44880</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44495</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44508</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44740</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44483</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44442</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44457</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44617</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44426</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44416</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44476</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44515</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44543</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44726</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44495</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44426</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44606</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44599</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44599</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44470</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44389</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44551</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44651</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44876</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44393</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44671</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44613</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44474</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>44746</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44466</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44376</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44412</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44496</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>44420</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44397</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44396</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44463</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>44750</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44610</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44494</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44379</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44568</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44420</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44704</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44781</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44522</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44532</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44532</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44579</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44610</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44711</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44498</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44439</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44491</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44438</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44489</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44489</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44769</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44860</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44596</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44427</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44483</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44573</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44502</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44812</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44712</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44508</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44452</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44427</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44603</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44820</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44820</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44434</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44596</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44537</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44574</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44537</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45386</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45420</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44571</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44802</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44573</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45477</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44489</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44967</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45324</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44487</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44894</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44915</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44523</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44595</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45330</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45594</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45594</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45594</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45594</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45250</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45594</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45048</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45715</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45236</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44592</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44406</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45460</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44502</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45463</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45722</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45672</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44537</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44764</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45230</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45594</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45594</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45554</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45557</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>45240</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45154</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45762</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45558</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45057</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45715</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45328</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45328</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45432</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45775</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44686</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45056</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45769</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45679</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>44988</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45152</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45330</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44991</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44900</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45322</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44656</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44970</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45181</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45397</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44713</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44532</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45632</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44908</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45033</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44602</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45194</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44922</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45446</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45400</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45058</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>44705</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45315</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44620</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45065</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44743</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45121</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44831</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45281</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45561</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44894</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45274</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45686</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45611</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45541</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45541</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44599</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45302</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45573</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45341</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44676</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45594</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45594</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45726</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45036</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45219</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45281</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45392</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45302</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45315</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45114</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45359</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45555</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45030</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45632</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45330</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45210</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45714</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45188</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45112</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44966</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45105</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45387</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45560</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45552</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45091</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45181</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45579</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45557</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44741</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45715</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>44687</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45691</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44473</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45071</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45557</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45558</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45594</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45583</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45408</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45594</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45594</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45586</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45309</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44854</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45436</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45260</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45211</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44560</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44545</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45737</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45091</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45693</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45176</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45176</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45764</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45390</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45124</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44909</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45644</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45385</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44812</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>44992</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45686</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45233</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45309</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45139</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45644</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45056</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44705</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45253</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44552</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45309</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45244</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45581</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44609</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44652</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44956</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45300</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45211</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45300</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45342</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>44858</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44814</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44814</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45061</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45049</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45244</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45629</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45599</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45280</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45145</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45412</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45210</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44845</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44929</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45372</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45533</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45169</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44711</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44746</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>44986</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>44896</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45153</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44938</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44741</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44981</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45338</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44960</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45019</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44843</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44434</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45194</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45104</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45702</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45769</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45387</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45714</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45246</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45140</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45665</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45112</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44874</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>44874</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45244</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45219</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44384</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>44959</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45232</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45113</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45705</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45579</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45078</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45168</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45513</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45737</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45108</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45215</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44532</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44427</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44600</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45412</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45412</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44386</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45166</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45757</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45316</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45316</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45623</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45551</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45224</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45194</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>44641</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>44896</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45222</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45244</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45601</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45070</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45162</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45162</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45090</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44679</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45128</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45128</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45611</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45259</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45309</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45309</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45679</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45009</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45304</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>45740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45316</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45686</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44866</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45103</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45140</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44858</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45253</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45446</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45392</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45250</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44529</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45016</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45686</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45686</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45670</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45278</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45166</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45250</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44397</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44986</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45245</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45345</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44915</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44972</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44749</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45468</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45127</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44678</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>44915</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45463</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44998</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45183</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45104</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44977</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45304</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45190</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45114</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45114</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45181</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45090</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44867</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45279</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45597</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45753</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45273</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45468</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44880</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45676</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45127</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45288</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45022</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>44869</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44426</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45401</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45236</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45236</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45317</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45392</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45685</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45608</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44894</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45638</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45121</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45121</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45121</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44950</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45169</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44928</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45036</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45568</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44998</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45061</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45217</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44677</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45763</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45089</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45236</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45085</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45392</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44609</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>44904</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>44904</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>44457</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45342</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45189</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45189</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44909</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45190</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45714</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44599</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45812</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45614</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45420</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45722</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45560</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45692</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45384</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45504</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45817</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45818</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45611</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45679</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45583</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45769</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45679</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45753</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45030</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45448</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45294</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45820</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45617</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45820</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45818</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45300</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45825</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45825</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45324</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45029</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45824</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45824</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44651</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44774</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45219</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45128</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45128</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45147</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45111</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44536</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45719</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44393</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45533</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45827</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45638</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44732</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45147</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45386</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45216</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45831</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45392</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45165</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45392</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45831</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45103</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45103</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45103</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45350</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45832</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45141</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45141</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45247</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45559</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45579</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45805</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45835</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45427</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45250</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45835</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45733</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45835</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45198</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44496</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44552</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45579</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45180</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45580</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>44761</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45840</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45477</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45559</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45540</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45153</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45754</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45421</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44424</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45754</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44811</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>45113</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45113</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45847</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44379</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45390</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>45853</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45012</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>45644</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44896</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45014</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44897</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45127</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45740</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45538</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44903</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44502</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45014</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45743</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44867</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45267</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45538</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45384</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45097</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45301</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>45552</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45247</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45782</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45534</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45702</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>45219</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44676</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45511</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45121</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45121</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45121</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45440</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44922</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45048</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45645</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45874</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45205</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45281</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45692</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45028</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45777</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45777</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45194</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44501</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>45855</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44995</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44876</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45547</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45777</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45161</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45240</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45495</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>44963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45106</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45780</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45780</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45385</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45385</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45754</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>44900</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44473</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45199</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45622</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45288</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45229</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45478</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45278</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>45546</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45783</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45782</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>45780</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45883</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45201</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>44494</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>45280</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45225</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45127</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45534</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45933</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44894</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45108</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44880</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44781</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45754</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45224</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45161</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45937</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>44711</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44782</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45572</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45937</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44487</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45896</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45204</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>45889</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45642</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>44547</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45816</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45890</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45895</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45894</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45443</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45726</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45139</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45856</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45373</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45897</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>45614</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44452</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45716</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45608</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>45946</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45950</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45369</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45923</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45127</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45127</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45902</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45372</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45219</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45810</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45594</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45594</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>44690</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45952</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45719</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45645</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45835</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45902</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45902</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45905</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45905</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45385</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45909</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45702</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45000</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45446</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>44858</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45594</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45594</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45594</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45594</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45594</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45594</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45302</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45302</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45911</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>44959</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>45910</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45787</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45958</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>44894</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45267</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45716</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45791</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45198</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>44651</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45946</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>45953</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>45540</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45509</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45916</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>45964</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45447</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45918</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45918</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45924</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45918</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>45918</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45918</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45918</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45378</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45918</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45495</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45446</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45008</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>44739</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45924</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45971</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45925</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45924</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45924</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45973</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45973</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45797</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>45796</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45979</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44824</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45979</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45980</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45574</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45764</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45803</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45993</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45993</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45665</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45988</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>45749</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45995</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45805</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45999</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45763</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>46000</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>46001</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46007</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>46008</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>46010</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>46010</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46010</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46010</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46010</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>46019</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52328,7 +52328,7 @@
         <v>46019</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>46029</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46029</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46031</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46031</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>46035</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46035</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>46035</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>46036</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>46036</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52923,7 +52923,7 @@
         <v>46036</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52980,7 +52980,7 @@
         <v>46036</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>45921</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46041</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>46043</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>46045</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>46045</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46049</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53379,7 +53379,7 @@
         <v>46048</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>46049</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46049</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>46049</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>46051</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>46057</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>46056</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>46057</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>46056</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>46057</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>46056</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>46059</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54063,7 +54063,7 @@
         <v>46059</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54120,7 +54120,7 @@
         <v>46059</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46061</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>46073</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46073</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>46072</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>46075</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54462,7 +54462,7 @@
         <v>46079</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>46079</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>46084</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46084</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54690,7 +54690,7 @@
         <v>46083</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>46083</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>46083</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>46083</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46083</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>46087</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>46097</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>46100</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46100</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55260,7 +55260,7 @@
         <v>46100</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>46099</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>46100</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46100</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46108</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>46107</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46108</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46112</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>46112</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>44769</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>44769</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>46112</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55954,7 +55954,7 @@
         <v>46113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>46161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>46162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56125,7 +56125,7 @@
         <v>46162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45594</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>46162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>45594</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56363,7 +56363,7 @@
         <v>46162</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56420,7 +56420,7 @@
         <v>46119</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56534,7 +56534,7 @@
         <v>46163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56591,7 +56591,7 @@
         <v>46163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>46163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46163</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>46163</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46163</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46168</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>46167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46125</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>46168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>46170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>46170</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>46171</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>46129</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46171</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57503,7 +57503,7 @@
         <v>46134</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>45881</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57617,7 +57617,7 @@
         <v>46134</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>46134</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46134</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>45677</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>45582</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45923</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45939</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>44468</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>45894</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45923</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45883</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45883</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45827</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45638</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45743</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45791</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45670</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45833</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45782</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45909</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45775</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45835</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45841</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>46139</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58985,7 +58985,7 @@
         <v>45826</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45960</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>45426</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45905</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45846</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45698</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59332,7 +59332,7 @@
         <v>45827</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45818</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45810</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>44522</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46183</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59622,7 +59622,7 @@
         <v>46183</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45686</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>44577</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45419</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59907,7 +59907,7 @@
         <v>45877</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46183</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60021,7 +60021,7 @@
         <v>46183</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>46183</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46188</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>46189</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>46146</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>46146</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46146</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>46147</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>46147</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>46147</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46147</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46147</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>46021</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>46191</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46149</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>46191</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>46191</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>46190</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>46021</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46021</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45397</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>46021</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46021</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61332,7 +61332,7 @@
         <v>46191</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46191</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>46148</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>46021</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>46021</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>46153</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61674,7 +61674,7 @@
         <v>46195</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>46188</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>45995</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45789</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45517</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45631</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>46198</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46198</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46198</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>46199</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46198</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46188</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62358,7 +62358,7 @@
         <v>46199</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45888</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45127</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45384</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45812</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46199</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46188</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44433</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44958</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45294</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45356</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45344</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>46098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44445</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>45883</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45649</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>46147</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>46161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45093</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45687</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45545</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45554</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44704</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>45348</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45351</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45674</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44721</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44704</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44645</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45280</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>44741</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44872</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45688</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45643</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45098</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45533</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45369</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>45279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45964</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>46199</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>46161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45428</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>46182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45327</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45606</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>44634</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44712</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44950</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45436</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45726</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45805</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44693</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44458</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44518</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44536</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44438</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44434</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44463</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44519</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44501</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44814</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44645</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44438</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44446</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44643</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44515</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44578</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44803</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44470</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44590</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44814</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44442</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>44769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44474</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44880</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44515</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44599</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44416</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44476</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44651</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44876</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44671</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44466</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44750</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44568</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44420</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44427</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44442</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44543</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44426</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>44606</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44470</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44613</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44474</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44746</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44412</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44420</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44610</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44610</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44491</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44740</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44483</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44617</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44457</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44726</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44468</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44551</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44599</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44463</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44781</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44494</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>44704</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>44522</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44532</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44532</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44498</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44439</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45446</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>44434</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>44574</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>44904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44904</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>44963</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44963</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44963</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44596</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>44571</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45468</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44712</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45127</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44579</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>44489</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44854</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44487</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44711</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44438</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44769</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44603</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44652</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45111</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44434</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45154</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>44502</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44812</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45145</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45294</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>44452</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45342</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45330</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>44427</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>44537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44609</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44489</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44489</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45477</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44545</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44473</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44483</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45183</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44560</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44508</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45488</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>44474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45124</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>44820</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44820</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45121</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44880</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45420</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45253</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44845</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44922</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>44426</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45161</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45412</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44741</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>44741</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45194</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>44537</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45288</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>45219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>45070</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>44814</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44814</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44998</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44592</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44741</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45103</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45715</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45229</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44896</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45222</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45754</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45754</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44424</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44487</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44867</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45280</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45148</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44880</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45201</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45190</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45622</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45240</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45219</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45315</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45573</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45883</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44867</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44599</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45259</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44874</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45392</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45672</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45056</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44896</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45225</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44894</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45559</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45300</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45302</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44532</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45127</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45386</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45359</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45302</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45390</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45386</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45392</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45392</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45446</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44986</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44595</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45555</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44903</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44938</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45432</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44547</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45014</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45317</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45236</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45112</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45894</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45890</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45477</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45856</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45412</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45412</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45895</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45594</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45594</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45594</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45897</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45140</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45552</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45378</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45645</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45534</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45719</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45560</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45369</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45902</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45902</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44599</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44869</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45791</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45902</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45230</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45810</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45338</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45835</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45244</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45408</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45222</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45419</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45169</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45583</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44843</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45392</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45905</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44670</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44894</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45910</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45909</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45909</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44711</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45071</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45583</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45787</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45757</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45582</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45384</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45911</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45345</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45916</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45579</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45540</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44970</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45894</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45918</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45245</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45918</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45918</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45918</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45918</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45918</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>45918</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>44522</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>44963</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45764</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45722</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44963</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45463</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45924</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45924</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45594</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45594</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45594</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45594</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45594</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45594</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45594</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45586</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45925</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45180</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45714</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45670</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45250</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45597</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45219</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45629</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45328</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45328</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44494</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45061</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45329</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45638</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44577</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45611</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>44743</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>45937</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45572</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44711</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45937</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45224</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44966</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45089</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45304</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>44972</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>44972</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45519</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45702</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46146</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>46146</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46146</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46147</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>46147</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46148</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44967</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45029</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>44992</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45552</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45199</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45012</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>46147</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46147</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45397</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>46147</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45896</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44981</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45147</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>46021</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46021</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45166</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44501</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46021</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>46021</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46021</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>44998</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>45557</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>46149</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>46021</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>46021</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45385</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45385</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45495</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45103</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45103</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45103</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45324</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45558</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46153</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45538</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45950</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45114</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45114</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44739</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45128</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>45952</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45923</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45554</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>44761</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45568</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>44774</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45692</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>46195</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45033</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>46198</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>46198</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>46198</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45468</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45946</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45121</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45995</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>44782</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45645</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45127</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>45953</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45057</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>45517</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45460</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45924</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45427</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44995</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45964</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>44536</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45400</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45594</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45631</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45789</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44427</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45692</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>45714</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>46198</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44858</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>44502</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45091</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>45030</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>45971</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46199</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45973</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45446</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45691</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44812</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45715</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45048</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44977</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45009</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45973</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>45190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44991</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45513</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45623</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45679</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>46199</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>46199</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>46161</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43537,7 +43537,7 @@
         <v>46199</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>44602</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>44732</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45979</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>46162</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45979</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45210</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45980</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>46162</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>46162</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>44909</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>45176</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>44922</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>45753</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45780</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>44552</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45250</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>46162</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45141</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>45614</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45533</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44529</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44641</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>46206</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>46163</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46163</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>44956</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>44874</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>46163</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>46163</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45715</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45111</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>45714</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45267</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45281</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>44894</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45090</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45019</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45611</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46467,7 +46467,7 @@
         <v>45676</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45162</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>45162</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>46205</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>46205</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45581</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45504</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45036</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45599</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>44523</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45233</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44600</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>44502</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44457</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45812</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>45993</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45993</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46163</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45632</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>44473</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45988</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45153</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>44713</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>46163</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44908</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>44897</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45999</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45204</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46168</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45737</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44896</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>46000</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45933</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45557</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>44928</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>46001</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>46167</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>46210</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45279</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>46168</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45273</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>46210</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45665</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45436</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45106</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45762</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45153</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45090</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45679</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45561</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>46008</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45392</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46007</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45447</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45296</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45211</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45617</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45104</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>46010</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45769</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>46010</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>46100</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45216</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>44687</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>45078</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45726</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51466,7 +51466,7 @@
         <v>46112</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>46171</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>45341</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45211</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45632</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>46099</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45232</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45127</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46171</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45139</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46170</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45373</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45538</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45128</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45128</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>45448</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>46170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>45022</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45693</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45555</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>46010</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45309</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>45309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>46019</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45387</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>46019</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>46171</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45240</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45121</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>45121</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45121</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>46029</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45387</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>44959</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46029</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46031</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46031</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
         <v>45030</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45236</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45166</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45108</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46036</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46035</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46035</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>45921</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>46036</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>45446</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>46035</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>46036</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>45392</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45324</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>46041</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55297,7 +55297,7 @@
         <v>45169</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55370,7 +55370,7 @@
         <v>46134</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45558</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>45309</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>45309</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55662,7 +55662,7 @@
         <v>46134</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>46043</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55808,7 +55808,7 @@
         <v>46048</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55881,7 +55881,7 @@
         <v>46045</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55954,7 +55954,7 @@
         <v>45113</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>46045</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45037</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45037</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>46199</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>45608</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45205</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56465,7 +56465,7 @@
         <v>45222</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>46049</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>44988</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45070</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56757,7 +56757,7 @@
         <v>45127</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>46049</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>46049</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>46049</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>46134</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46051</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>45048</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>46183</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46170</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>44900</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>46183</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>46056</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>44900</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57706,7 +57706,7 @@
         <v>45638</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>46056</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57852,7 +57852,7 @@
         <v>46056</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
         <v>45685</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>46183</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>46183</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45611</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>45161</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58290,7 +58290,7 @@
         <v>46057</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58363,7 +58363,7 @@
         <v>46057</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58436,7 +58436,7 @@
         <v>46183</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58509,7 +58509,7 @@
         <v>46057</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>44866</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>46059</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58728,7 +58728,7 @@
         <v>46183</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58801,7 +58801,7 @@
         <v>44532</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58874,7 +58874,7 @@
         <v>46061</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58947,7 +58947,7 @@
         <v>45139</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>46059</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>46059</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59166,7 +59166,7 @@
         <v>45112</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59239,7 +59239,7 @@
         <v>45181</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45580</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59385,7 +59385,7 @@
         <v>45014</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>46163</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45316</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45330</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>45219</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45330</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46188</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>45644</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>46232</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>45198</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60125,7 +60125,7 @@
         <v>46189</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60198,7 +60198,7 @@
         <v>45008</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>44929</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>45000</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>44609</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45733</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60568,7 +60568,7 @@
         <v>45722</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>45036</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>46232</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>46188</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60860,7 +60860,7 @@
         <v>46188</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45065</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61006,7 +61006,7 @@
         <v>44656</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>45443</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>45028</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61225,7 +61225,7 @@
         <v>45594</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>45594</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>45594</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>45594</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45594</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61615,7 +61615,7 @@
         <v>46191</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>45147</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61761,7 +61761,7 @@
         <v>46072</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61834,7 +61834,7 @@
         <v>46191</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61907,7 +61907,7 @@
         <v>46073</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45217</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>46073</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62126,7 +62126,7 @@
         <v>46075</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62199,7 +62199,7 @@
         <v>44831</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>46191</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45509</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62418,7 +62418,7 @@
         <v>45644</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>45194</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62564,7 +62564,7 @@
         <v>45594</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62642,7 +62642,7 @@
         <v>45594</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>45594</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62798,7 +62798,7 @@
         <v>46191</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>45219</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62944,7 +62944,7 @@
         <v>45601</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63017,7 +63017,7 @@
         <v>46190</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63090,7 +63090,7 @@
         <v>46079</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>46191</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45316</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63309,7 +63309,7 @@
         <v>45316</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>46079</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45056</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>46083</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63601,7 +63601,7 @@
         <v>45280</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63674,7 +63674,7 @@
         <v>46083</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>46083</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45705</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63898,7 +63898,7 @@
         <v>44858</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         <v>46083</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>46083</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64117,7 +64117,7 @@
         <v>46084</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64190,7 +64190,7 @@
         <v>45372</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>44764</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64336,7 +64336,7 @@
         <v>45541</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64409,7 +64409,7 @@
         <v>45091</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64487,7 +64487,7 @@
         <v>45579</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64560,7 +64560,7 @@
         <v>45016</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>46087</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -64706,7 +64706,7 @@
         <v>45385</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45385</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>45061</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>45560</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>45440</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>44909</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45679</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>45215</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>44876</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>44986</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45686</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45737</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>45224</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45495</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>45210</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45754</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45304</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>45244</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>44679</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>44678</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45775</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45244</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>44705</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>46099</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45250</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>44802</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46100</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46100</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>45420</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>45140</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46100</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>46100</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>45686</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>45686</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>45557</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>45579</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67354,7 +67354,7 @@
         <v>45533</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>45085</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67500,7 +67500,7 @@
         <v>46107</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67573,7 +67573,7 @@
         <v>45579</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67646,7 +67646,7 @@
         <v>45702</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>44676</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -67797,7 +67797,7 @@
         <v>44620</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -67870,7 +67870,7 @@
         <v>44769</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -67948,7 +67948,7 @@
         <v>44769</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68026,7 +68026,7 @@
         <v>46108</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>46108</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68172,7 +68172,7 @@
         <v>45253</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45247</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68318,7 +68318,7 @@
         <v>45165</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68391,7 +68391,7 @@
         <v>44676</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68469,7 +68469,7 @@
         <v>45397</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68542,7 +68542,7 @@
         <v>46113</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68615,7 +68615,7 @@
         <v>45236</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68688,7 +68688,7 @@
         <v>45236</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -68761,7 +68761,7 @@
         <v>46112</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -68834,7 +68834,7 @@
         <v>46112</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -68907,7 +68907,7 @@
         <v>45194</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -68980,7 +68980,7 @@
         <v>45114</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69053,7 +69053,7 @@
         <v>45547</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69126,7 +69126,7 @@
         <v>45679</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>45777</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69277,7 +69277,7 @@
         <v>45519</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69350,7 +69350,7 @@
         <v>45777</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69428,7 +69428,7 @@
         <v>44690</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69501,7 +69501,7 @@
         <v>44705</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69574,7 +69574,7 @@
         <v>45594</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69652,7 +69652,7 @@
         <v>44651</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -69725,7 +69725,7 @@
         <v>46119</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -69798,7 +69798,7 @@
         <v>45777</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -69876,7 +69876,7 @@
         <v>45460</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -69949,7 +69949,7 @@
         <v>45594</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70027,7 +70027,7 @@
         <v>45421</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70100,7 +70100,7 @@
         <v>45188</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70173,7 +70173,7 @@
         <v>45176</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>45780</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70319,7 +70319,7 @@
         <v>45780</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70392,7 +70392,7 @@
         <v>45121</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70465,7 +70465,7 @@
         <v>45782</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70538,7 +70538,7 @@
         <v>45250</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70611,7 +70611,7 @@
         <v>45546</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70684,7 +70684,7 @@
         <v>44746</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -70757,7 +70757,7 @@
         <v>45753</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -70830,7 +70830,7 @@
         <v>45783</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -70903,7 +70903,7 @@
         <v>45534</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45478</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71049,7 +71049,7 @@
         <v>45288</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71122,7 +71122,7 @@
         <v>45642</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71195,7 +71195,7 @@
         <v>46129</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71268,7 +71268,7 @@
         <v>44781</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71346,7 +71346,7 @@
         <v>44686</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>45608</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71492,7 +71492,7 @@
         <v>46134</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71565,7 +71565,7 @@
         <v>45260</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71638,7 +71638,7 @@
         <v>44915</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -71711,7 +71711,7 @@
         <v>44651</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -71784,7 +71784,7 @@
         <v>44831</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -71857,7 +71857,7 @@
         <v>45108</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -71930,7 +71930,7 @@
         <v>45881</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>45638</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72076,7 +72076,7 @@
         <v>45301</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72149,7 +72149,7 @@
         <v>45677</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72222,7 +72222,7 @@
         <v>45247</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72295,7 +72295,7 @@
         <v>45716</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72368,7 +72368,7 @@
         <v>45835</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72441,7 +72441,7 @@
         <v>45743</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72514,7 +72514,7 @@
         <v>45309</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72587,7 +72587,7 @@
         <v>45121</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72660,7 +72660,7 @@
         <v>44677</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -72733,7 +72733,7 @@
         <v>45827</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -72806,7 +72806,7 @@
         <v>44811</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -72879,7 +72879,7 @@
         <v>45698</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -72952,7 +72952,7 @@
         <v>44749</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73025,7 +73025,7 @@
         <v>45810</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73103,7 +73103,7 @@
         <v>45826</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73181,7 +73181,7 @@
         <v>45104</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73254,7 +73254,7 @@
         <v>45670</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73327,7 +73327,7 @@
         <v>45905</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73400,7 +73400,7 @@
         <v>45923</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73473,7 +73473,7 @@
         <v>45614</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73546,7 +73546,7 @@
         <v>45833</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73619,7 +73619,7 @@
         <v>45883</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73692,7 +73692,7 @@
         <v>45883</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -73765,7 +73765,7 @@
         <v>45775</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -73838,7 +73838,7 @@
         <v>45846</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -73911,7 +73911,7 @@
         <v>44894</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -73984,7 +73984,7 @@
         <v>44452</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74057,7 +74057,7 @@
         <v>45782</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74130,7 +74130,7 @@
         <v>44496</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74203,7 +74203,7 @@
         <v>45923</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74276,7 +74276,7 @@
         <v>45426</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74349,7 +74349,7 @@
         <v>45939</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74422,7 +74422,7 @@
         <v>44858</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74495,7 +74495,7 @@
         <v>45827</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74568,7 +74568,7 @@
         <v>45716</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74641,7 +74641,7 @@
         <v>45274</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -74714,7 +74714,7 @@
         <v>45246</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -74787,7 +74787,7 @@
         <v>45841</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -74860,7 +74860,7 @@
         <v>45743</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -74933,7 +74933,7 @@
         <v>45686</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75006,7 +75006,7 @@
         <v>44468</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75079,7 +75079,7 @@
         <v>45198</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75152,7 +75152,7 @@
         <v>45644</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75225,7 +75225,7 @@
         <v>45128</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75298,7 +75298,7 @@
         <v>45877</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75371,7 +75371,7 @@
         <v>45686</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75444,7 +75444,7 @@
         <v>45278</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75517,7 +75517,7 @@
         <v>45559</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75590,7 +75590,7 @@
         <v>45181</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75663,7 +75663,7 @@
         <v>45141</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -75736,7 +75736,7 @@
         <v>45194</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -75809,7 +75809,7 @@
         <v>45302</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -75882,7 +75882,7 @@
         <v>45726</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -75955,7 +75955,7 @@
         <v>45401</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76028,7 +76028,7 @@
         <v>45244</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76101,7 +76101,7 @@
         <v>45791</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76174,7 +76174,7 @@
         <v>45152</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76247,7 +76247,7 @@
         <v>45702</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76320,7 +76320,7 @@
         <v>45796</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76393,7 +76393,7 @@
         <v>45541</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76466,7 +76466,7 @@
         <v>45300</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76539,7 +76539,7 @@
         <v>45300</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76612,7 +76612,7 @@
         <v>45342</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -76685,7 +76685,7 @@
         <v>45302</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -76758,7 +76758,7 @@
         <v>45322</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -76831,7 +76831,7 @@
         <v>45511</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -76904,7 +76904,7 @@
         <v>44915</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -76977,7 +76977,7 @@
         <v>45764</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77050,7 +77050,7 @@
         <v>45574</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77123,7 +77123,7 @@
         <v>45665</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77196,7 +77196,7 @@
         <v>44824</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77269,7 +77269,7 @@
         <v>45749</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77342,7 +77342,7 @@
         <v>45803</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77415,7 +77415,7 @@
         <v>45805</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77488,7 +77488,7 @@
         <v>45763</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77561,7 +77561,7 @@
         <v>45447</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77634,7 +77634,7 @@
         <v>45769</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -77707,7 +77707,7 @@
         <v>45820</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -77780,7 +77780,7 @@
         <v>45820</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -77853,7 +77853,7 @@
         <v>45820</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -77926,7 +77926,7 @@
         <v>45817</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -77999,7 +77999,7 @@
         <v>45818</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78072,7 +78072,7 @@
         <v>45824</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78145,7 +78145,7 @@
         <v>45824</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78218,7 +78218,7 @@
         <v>45825</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78291,7 +78291,7 @@
         <v>45827</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78364,7 +78364,7 @@
         <v>45831</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78437,7 +78437,7 @@
         <v>45831</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78510,7 +78510,7 @@
         <v>45805</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78583,7 +78583,7 @@
         <v>45832</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78656,7 +78656,7 @@
         <v>45835</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -78729,7 +78729,7 @@
         <v>45835</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -78802,7 +78802,7 @@
         <v>45835</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -78875,7 +78875,7 @@
         <v>45840</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -78948,7 +78948,7 @@
         <v>45540</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79021,7 +79021,7 @@
         <v>45846</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79094,7 +79094,7 @@
         <v>45847</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79167,7 +79167,7 @@
         <v>45390</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79240,7 +79240,7 @@
         <v>45853</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79313,7 +79313,7 @@
         <v>45740</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79386,7 +79386,7 @@
         <v>45384</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79459,7 +79459,7 @@
         <v>45097</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79537,7 +79537,7 @@
         <v>45267</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79610,7 +79610,7 @@
         <v>45782</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -79683,7 +79683,7 @@
         <v>45874</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -79756,7 +79756,7 @@
         <v>45855</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -79829,7 +79829,7 @@
         <v>45278</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -79902,7 +79902,7 @@
         <v>44715</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -79975,7 +79975,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80048,7 +80048,7 @@
         <v>44704</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80121,7 +80121,7 @@
         <v>44588</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80194,7 +80194,7 @@
         <v>44727</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80267,7 +80267,7 @@
         <v>44722</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80340,7 +80340,7 @@
         <v>44603</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80413,7 +80413,7 @@
         <v>44693</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80486,7 +80486,7 @@
         <v>44726</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80559,7 +80559,7 @@
         <v>44712</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>44722</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -80705,7 +80705,7 @@
         <v>44712</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -80778,7 +80778,7 @@
         <v>44704</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -80851,7 +80851,7 @@
         <v>44596</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -80924,7 +80924,7 @@
         <v>44704</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -80997,7 +80997,7 @@
         <v>44588</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81070,7 +81070,7 @@
         <v>44442</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81143,7 +81143,7 @@
         <v>45054</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81216,7 +81216,7 @@
         <v>45230</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81294,7 +81294,7 @@
         <v>44498</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81367,7 +81367,7 @@
         <v>45622</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81440,7 +81440,7 @@
         <v>45054</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81513,7 +81513,7 @@
         <v>45054</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81586,7 +81586,7 @@
         <v>45056</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81659,7 +81659,7 @@
         <v>45434</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -81732,7 +81732,7 @@
         <v>44468</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -81805,7 +81805,7 @@
         <v>45054</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -81878,7 +81878,7 @@
         <v>45407</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -81951,7 +81951,7 @@
         <v>44802</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82024,7 +82024,7 @@
         <v>45071</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82097,7 +82097,7 @@
         <v>44495</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82170,7 +82170,7 @@
         <v>44474</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82243,7 +82243,7 @@
         <v>45224</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82321,7 +82321,7 @@
         <v>44972</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82394,7 +82394,7 @@
         <v>44487</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82467,7 +82467,7 @@
         <v>45230</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82540,7 +82540,7 @@
         <v>44939</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82613,7 +82613,7 @@
         <v>45468</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -82686,7 +82686,7 @@
         <v>45218</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -82759,7 +82759,7 @@
         <v>45054</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -82832,7 +82832,7 @@
         <v>44930</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -82910,7 +82910,7 @@
         <v>44973</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -82983,7 +82983,7 @@
         <v>44908</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83076,7 +83076,7 @@
         <v>45583</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83149,7 +83149,7 @@
         <v>45054</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83222,7 +83222,7 @@
         <v>45054</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83295,7 +83295,7 @@
         <v>44908</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83368,7 +83368,7 @@
         <v>44972</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83441,7 +83441,7 @@
         <v>44978</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83514,7 +83514,7 @@
         <v>44887</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83587,7 +83587,7 @@
         <v>44909</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83660,7 +83660,7 @@
         <v>45408</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -83733,7 +83733,7 @@
         <v>44908</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>45054</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -83879,7 +83879,7 @@
         <v>45526</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -83952,7 +83952,7 @@
         <v>45436</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84025,7 +84025,7 @@
         <v>45485</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84098,7 +84098,7 @@
         <v>45727</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84171,7 +84171,7 @@
         <v>45740</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84244,7 +84244,7 @@
         <v>45726</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84317,7 +84317,7 @@
         <v>45797</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84390,7 +84390,7 @@
         <v>45805</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84463,7 +84463,7 @@
         <v>45831</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -84536,7 +84536,7 @@
         <v>45951</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -84609,7 +84609,7 @@
         <v>45958</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -84682,7 +84682,7 @@
         <v>45964</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -84755,7 +84755,7 @@
         <v>45965</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -84828,7 +84828,7 @@
         <v>45981</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
@@ -84906,7 +84906,7 @@
         <v>45988</v>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
@@ -84979,7 +84979,7 @@
         <v>46092</v>
       </c>
       <c r="E1109" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
@@ -85057,7 +85057,7 @@
         <v>46202</v>
       </c>
       <c r="E1110" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1110" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45888</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45812</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45127</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45384</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45081</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44958</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45294</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45490</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45344</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>46098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44445</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>45649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45554</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45447</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>46147</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45093</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45545</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>46161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46182</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44704</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45348</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45351</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44721</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44645</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45964</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45280</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45617</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>45606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44872</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45643</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>46045</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45428</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45280</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44705</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>45327</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45824</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44746</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>45098</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45533</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45279</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45594</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>45594</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>46161</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>46161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>46246</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>46199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44634</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44712</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>46100</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44812</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44458</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44518</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>44764</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>44438</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44519</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44501</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44814</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44438</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44446</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44645</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44643</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44515</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44814</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44480</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44578</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44470</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44466</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44739</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>44590</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44814</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44442</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44769</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44711</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44474</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44508</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44880</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44515</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44476</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44495</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44599</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44651</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44466</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44750</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44568</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44442</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44543</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44606</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44470</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44746</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44613</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44474</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44610</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44610</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44491</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>44740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>44483</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44457</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44726</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44468</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44551</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44599</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>44463</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44781</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44494</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>44522</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44704</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44532</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>44532</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44498</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44439</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44573</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44712</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44711</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>44438</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>44769</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44502</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44452</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44489</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44489</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44483</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44508</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44574</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44537</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44537</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44571</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44603</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>44596</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>44473</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>44560</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44474</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44820</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44820</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45194</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45219</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44814</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44814</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44741</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45715</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>45412</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44741</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>44741</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>45754</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>45754</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>44867</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45372</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>45259</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44874</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45780</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45780</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45392</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45782</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45952</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>44487</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45546</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45280</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>45783</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>44894</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>44880</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45534</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45201</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45281</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45300</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45622</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45240</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45478</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45302</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44781</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45946</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45225</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45108</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45302</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45716</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45386</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45127</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45392</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45392</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45614</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44986</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44894</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45432</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45716</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45754</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45317</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45236</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45112</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45477</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44547</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45446</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45894</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45890</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44904</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44904</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>44963</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44963</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44963</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45856</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45468</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45895</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45127</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45127</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45551</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44573</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45971</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45897</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44854</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45244</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45973</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44894</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45645</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45719</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45111</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45902</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45154</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45791</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45902</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45145</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45810</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45294</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45342</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45330</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44950</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45796</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45905</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45477</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>44545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45910</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45488</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45124</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45909</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>44880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44922</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45787</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45911</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45973</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45916</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45540</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44537</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45979</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45918</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45918</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45918</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45979</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44896</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45574</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45665</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45924</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45148</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45148</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45980</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>44824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45749</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45803</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45805</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45925</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45763</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45447</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45190</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45573</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>44867</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>44599</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45672</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45056</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>44896</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45559</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44532</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45937</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45390</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44595</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45555</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45769</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44903</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44938</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45993</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45820</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45993</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45820</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45988</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45820</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45014</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45818</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45999</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45824</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45412</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45412</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45824</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45950</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45140</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45552</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>46001</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45378</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45534</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45560</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45369</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44599</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44869</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45338</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45244</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45408</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45222</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45827</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45583</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45392</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44670</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45805</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>44711</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45071</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45583</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45835</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45757</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45384</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45345</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45579</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>44970</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45540</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45846</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45764</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45189</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45189</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45722</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44963</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45463</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45847</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45594</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>45594</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45594</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45594</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45594</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45594</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45594</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45594</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45586</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45390</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45281</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45853</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45180</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45740</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45714</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>45670</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>45250</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>45629</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45328</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>45328</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>44494</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>45384</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45097</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45267</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>45782</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45874</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>45638</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45611</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44743</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44711</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45855</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45224</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>44966</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45089</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44972</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44972</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>45519</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45702</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44967</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>46007</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36730,7 +36730,7 @@
         <v>45012</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45278</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44981</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45166</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>44998</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45161</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45385</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45385</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45495</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45229</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45103</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45103</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45103</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45222</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45558</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45538</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45114</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45114</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>44739</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45128</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>45568</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>44774</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45692</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45033</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45121</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44782</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45645</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45127</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45460</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44995</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45113</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44536</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45692</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45714</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>44858</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44502</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45091</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45030</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>46010</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>46010</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46010</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46019</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45691</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>46019</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>44812</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45715</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45048</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45190</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44991</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45513</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45210</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>44909</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44922</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45753</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>44552</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45250</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45141</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45614</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45533</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44529</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>44641</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>44874</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45715</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45111</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45714</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>46029</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45267</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>44894</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46029</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>46031</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>46031</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45036</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45599</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>44523</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45233</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>46036</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>46035</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44600</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46035</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45921</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46036</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44457</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>46035</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>46036</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>46041</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45632</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>44473</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45153</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>44713</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46043</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44908</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>46048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>44897</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>46045</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45737</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>46045</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>46049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45557</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>44928</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>46049</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>46049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>46049</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>45279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>46051</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45273</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>46056</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45436</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45106</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>46056</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>46056</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45090</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45561</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45392</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45447</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>46057</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45211</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45078</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>45726</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45341</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45127</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>46057</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>46057</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45538</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>45128</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45128</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45387</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46059</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>46061</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45240</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45121</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45121</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45121</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>46059</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>46059</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45387</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>44959</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45030</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45236</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45166</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45446</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45392</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45324</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45558</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45309</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45309</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45113</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45037</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45037</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45222</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>44988</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45127</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>46072</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46073</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>46073</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>46075</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45048</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>45638</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45685</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45611</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>46079</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>46079</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45161</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>46083</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>44866</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49142,7 +49142,7 @@
         <v>46083</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>46083</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>46083</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>46083</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>46084</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45139</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45112</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>46087</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45580</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45014</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45316</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45330</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45219</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45330</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45644</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45198</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45008</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45000</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>44609</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45733</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45722</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45036</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45065</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45028</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45594</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45594</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45594</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>45594</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45594</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45509</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45644</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45594</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>45594</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>45594</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45601</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45316</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45316</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45056</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>44858</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>46099</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>46100</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>46100</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>46100</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>46100</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45372</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>44764</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45091</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         <v>45579</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45385</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45385</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>46107</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52930,7 +52930,7 @@
         <v>44769</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44769</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>46108</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45440</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45679</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53305,7 +53305,7 @@
         <v>46113</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53378,7 +53378,7 @@
         <v>46112</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>46112</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>45215</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>44876</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45495</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45594</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>46119</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>45210</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45754</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45594</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45244</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>44679</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>44678</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>45775</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>44802</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45420</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45140</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45686</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45686</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45085</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>44676</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>46129</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>44620</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55077,7 +55077,7 @@
         <v>45253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45247</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55223,7 +55223,7 @@
         <v>45881</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>44676</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>45638</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>45677</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45236</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>45236</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>45835</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45743</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>45827</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45698</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45810</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56036,7 +56036,7 @@
         <v>45826</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45114</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45670</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45905</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45679</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45923</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>45833</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45883</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>45883</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56698,7 +56698,7 @@
         <v>44690</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45775</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45846</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>44705</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>45782</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57063,7 +57063,7 @@
         <v>44651</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>45460</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45923</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45426</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>45421</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45188</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45939</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45827</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45176</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45121</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45250</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>44746</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45841</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>45686</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>44468</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58158,7 +58158,7 @@
         <v>45753</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58231,7 +58231,7 @@
         <v>45288</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>44686</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58377,7 +58377,7 @@
         <v>45260</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>45877</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>44915</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>44651</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45818</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>44831</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45301</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45247</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45309</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45121</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>44677</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>44811</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>44749</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>45104</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>44452</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59472,7 +59472,7 @@
         <v>44496</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>44858</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>45791</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>45246</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>45743</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45419</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45960</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>45198</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45644</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         <v>45128</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45686</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45278</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>45559</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45181</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>45141</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>45194</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>45302</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45726</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60859,7 +60859,7 @@
         <v>45401</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45244</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>45152</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45702</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>45541</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>45300</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45300</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>45342</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45302</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61516,7 +61516,7 @@
         <v>45322</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61589,7 +61589,7 @@
         <v>45511</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>44915</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>44652</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>45909</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>44537</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>44609</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>45183</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>45121</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45420</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>45253</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>44845</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>45582</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>44915</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>44552</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>45070</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>44998</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>44592</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45103</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>45058</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62976,7 +62976,7 @@
         <v>45315</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>45315</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>44979</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45386</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>45359</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>44959</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63414,7 +63414,7 @@
         <v>45594</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63492,7 +63492,7 @@
         <v>45594</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>45594</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63648,7 +63648,7 @@
         <v>45230</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>44843</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63794,7 +63794,7 @@
         <v>44894</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63867,7 +63867,7 @@
         <v>45245</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63940,7 +63940,7 @@
         <v>44963</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45597</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64086,7 +64086,7 @@
         <v>45219</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64159,7 +64159,7 @@
         <v>45061</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64232,7 +64232,7 @@
         <v>45572</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64305,7 +64305,7 @@
         <v>45304</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>45029</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64451,7 +64451,7 @@
         <v>44992</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45552</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45199</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45181</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>45147</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -64816,7 +64816,7 @@
         <v>45105</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -64889,7 +64889,7 @@
         <v>44501</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -64962,7 +64962,7 @@
         <v>45557</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45324</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65108,7 +65108,7 @@
         <v>45894</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65181,7 +65181,7 @@
         <v>45554</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65254,7 +65254,7 @@
         <v>44761</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>45468</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
         <v>45057</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45427</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45400</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45594</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65702,7 +65702,7 @@
         <v>45446</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65775,7 +65775,7 @@
         <v>44977</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -65848,7 +65848,7 @@
         <v>45009</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -65926,7 +65926,7 @@
         <v>45679</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -65999,7 +65999,7 @@
         <v>44602</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66072,7 +66072,7 @@
         <v>44732</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45176</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66218,7 +66218,7 @@
         <v>44956</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66291,7 +66291,7 @@
         <v>45281</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>44522</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45090</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45019</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>45611</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45676</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66734,7 +66734,7 @@
         <v>45162</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -66807,7 +66807,7 @@
         <v>45162</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -66880,7 +66880,7 @@
         <v>45581</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -66953,7 +66953,7 @@
         <v>45504</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>44502</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45049</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>44896</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>45665</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67323,7 +67323,7 @@
         <v>45762</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67401,7 +67401,7 @@
         <v>45153</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67474,7 +67474,7 @@
         <v>45679</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45296</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67620,7 +67620,7 @@
         <v>45617</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67693,7 +67693,7 @@
         <v>45769</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67766,7 +67766,7 @@
         <v>44687</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -67839,7 +67839,7 @@
         <v>45211</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -67912,7 +67912,7 @@
         <v>45632</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>45232</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68058,7 +68058,7 @@
         <v>45139</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>45373</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>45448</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45022</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45693</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>45555</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45309</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>45309</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68642,7 +68642,7 @@
         <v>45108</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68715,7 +68715,7 @@
         <v>45169</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68788,7 +68788,7 @@
         <v>45608</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -68861,7 +68861,7 @@
         <v>45205</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         <v>45329</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69007,7 +69007,7 @@
         <v>45070</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69080,7 +69080,7 @@
         <v>44577</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>44900</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>44900</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>44532</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69372,7 +69372,7 @@
         <v>45181</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69445,7 +69445,7 @@
         <v>46146</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>46146</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>46146</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>44929</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69742,7 +69742,7 @@
         <v>46147</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46147</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -69888,7 +69888,7 @@
         <v>46148</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -69961,7 +69961,7 @@
         <v>44656</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70034,7 +70034,7 @@
         <v>46147</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70107,7 +70107,7 @@
         <v>46147</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70180,7 +70180,7 @@
         <v>45397</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70253,7 +70253,7 @@
         <v>46147</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70326,7 +70326,7 @@
         <v>45443</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70399,7 +70399,7 @@
         <v>45147</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70472,7 +70472,7 @@
         <v>45217</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70545,7 +70545,7 @@
         <v>44831</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>45194</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70691,7 +70691,7 @@
         <v>45219</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70764,7 +70764,7 @@
         <v>46021</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -70837,7 +70837,7 @@
         <v>46149</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -70910,7 +70910,7 @@
         <v>45280</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -70983,7 +70983,7 @@
         <v>46021</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71056,7 +71056,7 @@
         <v>45705</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71134,7 +71134,7 @@
         <v>46153</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71207,7 +71207,7 @@
         <v>45016</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71280,7 +71280,7 @@
         <v>45061</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71353,7 +71353,7 @@
         <v>45560</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71426,7 +71426,7 @@
         <v>44909</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71504,7 +71504,7 @@
         <v>45995</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71577,7 +71577,7 @@
         <v>45517</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71650,7 +71650,7 @@
         <v>44986</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71723,7 +71723,7 @@
         <v>45686</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -71796,7 +71796,7 @@
         <v>45737</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -71869,7 +71869,7 @@
         <v>45224</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -71942,7 +71942,7 @@
         <v>45304</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72015,7 +72015,7 @@
         <v>45631</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72088,7 +72088,7 @@
         <v>45789</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72161,7 +72161,7 @@
         <v>45244</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72234,7 +72234,7 @@
         <v>45250</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72307,7 +72307,7 @@
         <v>45557</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72380,7 +72380,7 @@
         <v>45579</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72453,7 +72453,7 @@
         <v>45533</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72526,7 +72526,7 @@
         <v>45579</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72599,7 +72599,7 @@
         <v>45702</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72672,7 +72672,7 @@
         <v>45165</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72745,7 +72745,7 @@
         <v>45397</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -72818,7 +72818,7 @@
         <v>45194</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -72891,7 +72891,7 @@
         <v>45547</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>45777</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>45519</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>45777</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>45777</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73271,7 +73271,7 @@
         <v>45623</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73344,7 +73344,7 @@
         <v>46161</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73417,7 +73417,7 @@
         <v>46162</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73490,7 +73490,7 @@
         <v>46162</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73563,7 +73563,7 @@
         <v>46162</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>45780</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73709,7 +73709,7 @@
         <v>46162</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>45719</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -73855,7 +73855,7 @@
         <v>46163</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -73928,7 +73928,7 @@
         <v>46163</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74001,7 +74001,7 @@
         <v>46163</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         <v>46163</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>45812</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>46163</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74293,7 +74293,7 @@
         <v>46163</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74366,7 +74366,7 @@
         <v>46168</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>45933</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>46167</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>46168</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>46100</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>45216</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>46112</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46171</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>46099</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>46171</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>46170</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>46010</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>46171</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75315,7 +75315,7 @@
         <v>46134</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75388,7 +75388,7 @@
         <v>46134</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75461,7 +75461,7 @@
         <v>46134</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75534,7 +75534,7 @@
         <v>46183</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75607,7 +75607,7 @@
         <v>46170</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>46183</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75753,7 +75753,7 @@
         <v>46183</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -75826,7 +75826,7 @@
         <v>46183</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -75899,7 +75899,7 @@
         <v>46183</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -75972,7 +75972,7 @@
         <v>46183</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76045,7 +76045,7 @@
         <v>46163</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76118,7 +76118,7 @@
         <v>46188</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76191,7 +76191,7 @@
         <v>46232</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76264,7 +76264,7 @@
         <v>46189</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76337,7 +76337,7 @@
         <v>46232</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76410,7 +76410,7 @@
         <v>46188</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76483,7 +76483,7 @@
         <v>46188</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76556,7 +76556,7 @@
         <v>46191</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76629,7 +76629,7 @@
         <v>46191</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76702,7 +76702,7 @@
         <v>46191</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -76775,7 +76775,7 @@
         <v>46191</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -76848,7 +76848,7 @@
         <v>46190</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -76921,7 +76921,7 @@
         <v>46191</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -76994,7 +76994,7 @@
         <v>46195</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77067,7 +77067,7 @@
         <v>46108</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77140,7 +77140,7 @@
         <v>46237</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77213,7 +77213,7 @@
         <v>45924</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77286,7 +77286,7 @@
         <v>46237</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77359,7 +77359,7 @@
         <v>46239</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77432,7 +77432,7 @@
         <v>46199</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77505,7 +77505,7 @@
         <v>46244</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77583,7 +77583,7 @@
         <v>46199</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77656,7 +77656,7 @@
         <v>46198</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77729,7 +77729,7 @@
         <v>46198</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -77802,7 +77802,7 @@
         <v>46244</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -77875,7 +77875,7 @@
         <v>46244</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -77953,7 +77953,7 @@
         <v>46244</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78026,7 +78026,7 @@
         <v>46198</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78099,7 +78099,7 @@
         <v>46198</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78172,7 +78172,7 @@
         <v>45541</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78245,7 +78245,7 @@
         <v>46199</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78318,7 +78318,7 @@
         <v>46199</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78391,7 +78391,7 @@
         <v>46244</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78469,7 +78469,7 @@
         <v>46246</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78547,7 +78547,7 @@
         <v>46244</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78620,7 +78620,7 @@
         <v>46245</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78693,7 +78693,7 @@
         <v>46199</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78766,7 +78766,7 @@
         <v>46244</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -78844,7 +78844,7 @@
         <v>46244</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -78922,7 +78922,7 @@
         <v>46245</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -78995,7 +78995,7 @@
         <v>46244</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79073,7 +79073,7 @@
         <v>46205</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79146,7 +79146,7 @@
         <v>46205</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79219,7 +79219,7 @@
         <v>46252</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79292,7 +79292,7 @@
         <v>46206</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79370,7 +79370,7 @@
         <v>46252</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79443,7 +79443,7 @@
         <v>46210</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79521,7 +79521,7 @@
         <v>46253</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79594,7 +79594,7 @@
         <v>46210</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79672,7 +79672,7 @@
         <v>46258</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79745,7 +79745,7 @@
         <v>46260</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -79818,7 +79818,7 @@
         <v>46245</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -79891,7 +79891,7 @@
         <v>46170</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -79964,7 +79964,7 @@
         <v>46261</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80037,7 +80037,7 @@
         <v>46262</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80110,7 +80110,7 @@
         <v>44715</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80183,7 +80183,7 @@
         <v>44722</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80256,7 +80256,7 @@
         <v>44588</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80329,7 +80329,7 @@
         <v>44727</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80402,7 +80402,7 @@
         <v>44722</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80475,7 +80475,7 @@
         <v>44603</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80548,7 +80548,7 @@
         <v>44693</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80621,7 +80621,7 @@
         <v>44726</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80694,7 +80694,7 @@
         <v>44712</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80767,7 +80767,7 @@
         <v>44722</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -80840,7 +80840,7 @@
         <v>44712</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -80913,7 +80913,7 @@
         <v>44704</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -80986,7 +80986,7 @@
         <v>44596</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81059,7 +81059,7 @@
         <v>44704</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81132,7 +81132,7 @@
         <v>44588</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81205,7 +81205,7 @@
         <v>44442</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81278,7 +81278,7 @@
         <v>45054</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81351,7 +81351,7 @@
         <v>45230</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81429,7 +81429,7 @@
         <v>44498</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81502,7 +81502,7 @@
         <v>45622</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81575,7 +81575,7 @@
         <v>45054</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81648,7 +81648,7 @@
         <v>45054</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81721,7 +81721,7 @@
         <v>45056</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81794,7 +81794,7 @@
         <v>45434</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -81867,7 +81867,7 @@
         <v>44468</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -81940,7 +81940,7 @@
         <v>45054</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82013,7 +82013,7 @@
         <v>45407</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82086,7 +82086,7 @@
         <v>44802</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82159,7 +82159,7 @@
         <v>45071</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82232,7 +82232,7 @@
         <v>44495</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82305,7 +82305,7 @@
         <v>44474</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82378,7 +82378,7 @@
         <v>45224</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82456,7 +82456,7 @@
         <v>44972</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82529,7 +82529,7 @@
         <v>44487</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82602,7 +82602,7 @@
         <v>45230</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82675,7 +82675,7 @@
         <v>44939</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82748,7 +82748,7 @@
         <v>45468</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -82821,7 +82821,7 @@
         <v>45218</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -82894,7 +82894,7 @@
         <v>45054</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -82967,7 +82967,7 @@
         <v>44930</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83045,7 +83045,7 @@
         <v>44973</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83118,7 +83118,7 @@
         <v>44908</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83211,7 +83211,7 @@
         <v>45583</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83284,7 +83284,7 @@
         <v>45054</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83357,7 +83357,7 @@
         <v>45054</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83430,7 +83430,7 @@
         <v>44908</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83503,7 +83503,7 @@
         <v>44972</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83576,7 +83576,7 @@
         <v>44978</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83649,7 +83649,7 @@
         <v>44887</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83722,7 +83722,7 @@
         <v>44909</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83795,7 +83795,7 @@
         <v>45408</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -83868,7 +83868,7 @@
         <v>44908</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>45054</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84014,7 +84014,7 @@
         <v>45526</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84087,7 +84087,7 @@
         <v>45436</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84160,7 +84160,7 @@
         <v>45485</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84233,7 +84233,7 @@
         <v>45727</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84306,7 +84306,7 @@
         <v>45740</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84379,7 +84379,7 @@
         <v>45726</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84452,7 +84452,7 @@
         <v>45797</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84525,7 +84525,7 @@
         <v>45805</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84598,7 +84598,7 @@
         <v>45831</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -84671,7 +84671,7 @@
         <v>45951</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -84744,7 +84744,7 @@
         <v>45958</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -84817,7 +84817,7 @@
         <v>45964</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -84890,7 +84890,7 @@
         <v>45965</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -84963,7 +84963,7 @@
         <v>45981</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
@@ -85041,7 +85041,7 @@
         <v>45988</v>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
@@ -85114,7 +85114,7 @@
         <v>46092</v>
       </c>
       <c r="E1109" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
@@ -85192,7 +85192,7 @@
         <v>46202</v>
       </c>
       <c r="E1110" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
@@ -85265,7 +85265,7 @@
         <v>46262</v>
       </c>
       <c r="E1111" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1111" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45384</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45468</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45812</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44958</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45294</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45344</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>46098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44445</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>45554</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45883</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45874</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>46147</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>46161</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>46182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45587</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45447</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44704</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45348</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45351</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44721</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44645</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44705</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45617</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>45606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45643</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>45279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45280</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46045</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45428</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44746</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45327</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45824</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>45688</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>45098</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45280</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45369</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>46199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44634</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44712</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>46100</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44812</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44458</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44518</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>44764</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>44463</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44501</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44814</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44645</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44446</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44643</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44515</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44525</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44480</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44578</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44803</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44470</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44590</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44814</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44474</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44880</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44711</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44515</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44495</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44599</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44476</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44651</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44876</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44466</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44496</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44750</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44568</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44543</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44746</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44606</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44610</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44610</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44491</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44740</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44483</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44617</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44457</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>44726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>44468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44551</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44463</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44781</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44704</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44532</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>44498</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44860</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44596</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>44573</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44579</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44711</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>44502</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44812</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44452</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44489</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44483</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44508</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44574</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44537</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44571</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44489</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44603</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44596</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44473</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>44560</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>44474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44820</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>44820</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44802</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45386</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45236</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45420</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>44967</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45460</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44502</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45324</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45672</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44523</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45594</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45594</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45554</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44537</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45762</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45558</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44764</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45594</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45594</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45775</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45594</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45679</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45152</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45330</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44991</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44656</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44970</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45322</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45181</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45397</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44713</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>44979</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45033</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44602</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44532</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44620</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45561</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44894</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45541</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45726</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>44599</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45341</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45219</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45114</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45330</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45392</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45714</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45715</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45315</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45359</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45105</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45555</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45557</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45691</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45579</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45583</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45408</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45557</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45586</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45309</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45737</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>44854</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45460</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45211</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45686</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45233</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45300</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44814</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>44814</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45061</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44858</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45280</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45412</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45796</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44929</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45309</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45372</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44824</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44746</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>44896</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45222</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45574</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44981</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45754</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45253</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45622</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45229</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45019</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45278</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45764</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44552</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45803</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45309</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45244</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45244</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45714</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45140</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45219</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>46019</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45665</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>46019</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45749</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44959</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45805</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45280</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45763</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45168</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45127</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45447</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45222</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44880</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46029</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45162</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45162</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45090</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44679</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45128</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45611</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45304</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44963</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44963</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44963</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44866</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44487</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45817</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45769</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44529</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45686</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45278</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>44547</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45890</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45820</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45895</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45894</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45820</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45820</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45111</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45856</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>45825</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45245</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45897</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45824</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44678</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44915</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45902</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45810</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45104</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45831</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45719</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45835</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>46031</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45902</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45902</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45905</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45831</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45304</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45190</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45832</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45909</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45279</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45753</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45805</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>44537</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45236</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45236</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45835</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45317</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45911</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>46031</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45910</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45835</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45638</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45787</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45121</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45121</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45121</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45835</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45169</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45540</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45916</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45918</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45918</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45918</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>46035</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45924</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>45925</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45048</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45540</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45463</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45846</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45230</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45847</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45240</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45154</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45390</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45853</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>46035</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45715</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45328</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45328</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45769</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>46035</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45740</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>46036</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45937</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45937</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45632</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44908</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45896</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45267</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45194</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44922</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45384</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45097</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>46036</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45446</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>46036</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45058</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45921</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>46041</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45281</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45782</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45274</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45611</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45950</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45594</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45594</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45923</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45874</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45855</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45281</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45952</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>46045</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>46045</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45030</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45210</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45112</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>44966</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46049</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45883</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45387</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>46048</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>46049</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46049</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>46049</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45560</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45091</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>46051</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>44741</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44741</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45201</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45715</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>44687</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45946</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>46057</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>46056</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>46057</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46056</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45436</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45148</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45148</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44545</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45953</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45091</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46056</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45390</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45964</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45124</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45385</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45924</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46059</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>46059</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45240</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45342</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45971</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45049</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45244</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45629</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>46061</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45599</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45145</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45973</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45973</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44845</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45169</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>44711</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44938</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45104</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45702</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45979</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45979</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45387</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45980</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>46073</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46073</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>46072</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45113</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45579</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45513</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45215</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44532</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45224</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>46075</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>44641</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46079</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>46079</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45128</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>45259</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45309</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45309</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45488</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45009</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45993</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45993</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>45686</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45103</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>45988</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44858</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45253</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>46084</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>46083</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45999</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45250</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45016</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45670</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45250</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>46000</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>46083</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>46001</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>44986</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46083</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46083</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>46083</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>46007</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45183</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46008</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>44977</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>46010</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>46010</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45114</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>45114</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>46010</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45296</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>45090</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>44867</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45525,7 +45525,7 @@
         <v>45597</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>46087</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45401</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45685</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>44972</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>44928</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45568</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45061</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>44904</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>44904</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45420</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>45504</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45583</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>46100</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46100</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45753</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>46099</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>46100</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>46100</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46917,7 +46917,7 @@
         <v>45617</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46990,7 +46990,7 @@
         <v>44670</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45324</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45029</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>44651</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45533</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45147</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45392</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45392</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45103</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45103</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45103</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>45247</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45559</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45579</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46107</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>46108</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>46112</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45427</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>44769</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>45250</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45733</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>44769</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>46112</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         <v>44552</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>46113</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48830,7 +48830,7 @@
         <v>45180</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>45580</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>44761</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45594</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45594</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45477</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>46119</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>45559</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45153</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45421</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>44811</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45113</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45113</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>44896</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>46129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45538</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>44903</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>44502</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>45538</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45301</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45881</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>44595</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>45330</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45250</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>44592</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45722</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45557</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45677</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45582</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45923</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45432</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>44686</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>45939</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>44468</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51342,7 +51342,7 @@
         <v>45400</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51415,7 +51415,7 @@
         <v>44705</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45315</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45894</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45923</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45065</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45883</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>44743</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>45883</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45827</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>45121</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>44831</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45638</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>45743</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45791</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45302</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45573</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>44676</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45670</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45833</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>45036</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45782</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>45302</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>45909</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45775</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>45632</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45188</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45552</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45181</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45835</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45071</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45558</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45594</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45594</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>45594</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45841</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45826</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45960</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45426</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45693</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45905</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45764</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>45644</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45056</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45846</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45037</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45037</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45581</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>44609</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45698</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>44652</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>44956</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45300</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45211</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45827</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>45818</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45810</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>45210</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>45533</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>44986</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>44741</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45338</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>44960</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44522</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>44843</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45665</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45329</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45686</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>44874</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>44874</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>44963</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>44577</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45419</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>44600</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45412</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>45412</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>45757</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>45316</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45316</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45877</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45551</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         <v>44896</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45601</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>45679</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45316</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45140</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45446</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>45392</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45166</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46146</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46146</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46146</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45345</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>44915</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58254,7 +58254,7 @@
         <v>44972</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>46147</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46147</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46147</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46147</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46147</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>46021</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>44998</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>46149</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58911,7 +58911,7 @@
         <v>45397</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58984,7 +58984,7 @@
         <v>45468</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>46148</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59130,7 +59130,7 @@
         <v>46021</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>44880</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59276,7 +59276,7 @@
         <v>46153</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45676</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59427,7 +59427,7 @@
         <v>45127</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45288</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45022</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59646,7 +59646,7 @@
         <v>44869</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59719,7 +59719,7 @@
         <v>44998</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>45995</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45217</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59938,7 +59938,7 @@
         <v>45789</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45085</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>44609</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60157,7 +60157,7 @@
         <v>45517</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60230,7 +60230,7 @@
         <v>44457</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45631</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45722</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60449,7 +60449,7 @@
         <v>45560</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>44831</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60595,7 +60595,7 @@
         <v>45611</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45679</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60741,7 +60741,7 @@
         <v>46161</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45679</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60887,7 +60887,7 @@
         <v>45030</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60960,7 +60960,7 @@
         <v>45300</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61033,7 +61033,7 @@
         <v>44774</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61106,7 +61106,7 @@
         <v>45128</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45128</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>45111</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61325,7 +61325,7 @@
         <v>45638</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45623</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>45386</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61544,7 +61544,7 @@
         <v>46162</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45165</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>46163</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>46163</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61836,7 +61836,7 @@
         <v>45780</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61909,7 +61909,7 @@
         <v>46162</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>46163</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>46163</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>45555</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>46163</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>46162</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62347,7 +62347,7 @@
         <v>46163</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>45141</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>45141</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62566,7 +62566,7 @@
         <v>45719</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62639,7 +62639,7 @@
         <v>46162</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62712,7 +62712,7 @@
         <v>44496</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62785,7 +62785,7 @@
         <v>45579</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62858,7 +62858,7 @@
         <v>46167</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62931,7 +62931,7 @@
         <v>45754</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63004,7 +63004,7 @@
         <v>45812</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63077,7 +63077,7 @@
         <v>45754</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>46168</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>45012</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63296,7 +63296,7 @@
         <v>45222</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63369,7 +63369,7 @@
         <v>45127</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>46168</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         <v>45933</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>44867</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>46099</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         <v>46100</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>45552</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>46170</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63953,7 +63953,7 @@
         <v>46171</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64026,7 +64026,7 @@
         <v>45216</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64099,7 +64099,7 @@
         <v>45247</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64172,7 +64172,7 @@
         <v>45511</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64245,7 +64245,7 @@
         <v>44922</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64318,7 +64318,7 @@
         <v>46112</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64391,7 +64391,7 @@
         <v>45048</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
         <v>46171</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64537,7 +64537,7 @@
         <v>45205</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64610,7 +64610,7 @@
         <v>46010</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64683,7 +64683,7 @@
         <v>44501</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -64756,7 +64756,7 @@
         <v>46171</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>44995</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -64902,7 +64902,7 @@
         <v>44876</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -64980,7 +64980,7 @@
         <v>45495</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65053,7 +65053,7 @@
         <v>44963</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65126,7 +65126,7 @@
         <v>45106</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>45385</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65277,7 +65277,7 @@
         <v>45385</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65355,7 +65355,7 @@
         <v>44900</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>44473</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65501,7 +65501,7 @@
         <v>45199</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65574,7 +65574,7 @@
         <v>45070</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>44494</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65720,7 +65720,7 @@
         <v>46134</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45754</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -65866,7 +65866,7 @@
         <v>46134</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45224</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66012,7 +66012,7 @@
         <v>45161</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>44711</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>44782</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45572</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66309,7 +66309,7 @@
         <v>45204</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66382,7 +66382,7 @@
         <v>46134</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>45443</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66528,7 +66528,7 @@
         <v>45726</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66601,7 +66601,7 @@
         <v>45139</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>45373</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -66747,7 +66747,7 @@
         <v>46170</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>44452</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>45369</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -66966,7 +66966,7 @@
         <v>45127</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67039,7 +67039,7 @@
         <v>45127</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67112,7 +67112,7 @@
         <v>46183</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67185,7 +67185,7 @@
         <v>45372</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67258,7 +67258,7 @@
         <v>45219</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         <v>46183</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67404,7 +67404,7 @@
         <v>46183</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67477,7 +67477,7 @@
         <v>45594</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67555,7 +67555,7 @@
         <v>45594</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>44690</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>46183</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -67779,7 +67779,7 @@
         <v>46183</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>45385</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -67930,7 +67930,7 @@
         <v>45702</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68003,7 +68003,7 @@
         <v>45000</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68076,7 +68076,7 @@
         <v>45446</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>44858</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>46188</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45594</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>45594</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68451,7 +68451,7 @@
         <v>45594</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68529,7 +68529,7 @@
         <v>45594</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>45594</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68685,7 +68685,7 @@
         <v>45594</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68763,7 +68763,7 @@
         <v>45302</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -68836,7 +68836,7 @@
         <v>45302</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -68909,7 +68909,7 @@
         <v>44959</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -68982,7 +68982,7 @@
         <v>46188</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>44894</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45267</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45198</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>44651</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>46163</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>46188</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>45509</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69566,7 +69566,7 @@
         <v>46232</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69639,7 +69639,7 @@
         <v>45447</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69712,7 +69712,7 @@
         <v>46232</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>46189</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -69858,7 +69858,7 @@
         <v>46190</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -69931,7 +69931,7 @@
         <v>45378</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70004,7 +70004,7 @@
         <v>45495</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70077,7 +70077,7 @@
         <v>45446</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70150,7 +70150,7 @@
         <v>45008</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70223,7 +70223,7 @@
         <v>46191</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70296,7 +70296,7 @@
         <v>44739</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70369,7 +70369,7 @@
         <v>46191</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70442,7 +70442,7 @@
         <v>45924</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70515,7 +70515,7 @@
         <v>45519</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70588,7 +70588,7 @@
         <v>46108</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70661,7 +70661,7 @@
         <v>45176</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70734,7 +70734,7 @@
         <v>45176</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -70807,7 +70807,7 @@
         <v>46237</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -70880,7 +70880,7 @@
         <v>46191</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -70953,7 +70953,7 @@
         <v>46237</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71026,7 +71026,7 @@
         <v>45644</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71099,7 +71099,7 @@
         <v>46191</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71172,7 +71172,7 @@
         <v>44812</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71245,7 +71245,7 @@
         <v>44992</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         <v>45139</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71391,7 +71391,7 @@
         <v>46191</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46239</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>46195</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71610,7 +71610,7 @@
         <v>45244</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71683,7 +71683,7 @@
         <v>45232</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -71756,7 +71756,7 @@
         <v>45705</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -71834,7 +71834,7 @@
         <v>46198</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -71907,7 +71907,7 @@
         <v>45078</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -71985,7 +71985,7 @@
         <v>45737</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72058,7 +72058,7 @@
         <v>45108</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72131,7 +72131,7 @@
         <v>46198</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72204,7 +72204,7 @@
         <v>46198</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72277,7 +72277,7 @@
         <v>44749</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72350,7 +72350,7 @@
         <v>45468</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>45127</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72496,7 +72496,7 @@
         <v>46198</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72569,7 +72569,7 @@
         <v>45273</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72642,7 +72642,7 @@
         <v>46245</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72715,7 +72715,7 @@
         <v>46244</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -72788,7 +72788,7 @@
         <v>45392</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -72866,7 +72866,7 @@
         <v>45608</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -72939,7 +72939,7 @@
         <v>44894</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73012,7 +73012,7 @@
         <v>46199</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73085,7 +73085,7 @@
         <v>46245</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73158,7 +73158,7 @@
         <v>46244</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73236,7 +73236,7 @@
         <v>46244</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73314,7 +73314,7 @@
         <v>46244</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73392,7 +73392,7 @@
         <v>46199</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73465,7 +73465,7 @@
         <v>46244</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73543,7 +73543,7 @@
         <v>44677</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73616,7 +73616,7 @@
         <v>45089</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73689,7 +73689,7 @@
         <v>45236</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73762,7 +73762,7 @@
         <v>45392</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -73840,7 +73840,7 @@
         <v>46244</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -73913,7 +73913,7 @@
         <v>46244</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -73991,7 +73991,7 @@
         <v>46244</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>46244</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74142,7 +74142,7 @@
         <v>45342</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74215,7 +74215,7 @@
         <v>45189</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74288,7 +74288,7 @@
         <v>45189</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>44909</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>45190</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>45714</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>44599</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>45614</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>45692</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>45384</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46199</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>45541</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>46246</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75101,7 +75101,7 @@
         <v>45448</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75174,7 +75174,7 @@
         <v>46199</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75247,7 +75247,7 @@
         <v>46199</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75320,7 +75320,7 @@
         <v>45294</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75393,7 +75393,7 @@
         <v>45219</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75466,7 +75466,7 @@
         <v>45147</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75539,7 +75539,7 @@
         <v>44536</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75612,7 +75612,7 @@
         <v>44732</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75685,7 +75685,7 @@
         <v>46206</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
         <v>45198</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>46205</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -75909,7 +75909,7 @@
         <v>46205</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -75982,7 +75982,7 @@
         <v>45644</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76055,7 +76055,7 @@
         <v>46252</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76128,7 +76128,7 @@
         <v>45014</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76206,7 +76206,7 @@
         <v>44897</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76279,7 +76279,7 @@
         <v>45014</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76352,7 +76352,7 @@
         <v>45743</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76425,7 +76425,7 @@
         <v>46253</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76498,7 +76498,7 @@
         <v>46210</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76576,7 +76576,7 @@
         <v>46252</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76649,7 +76649,7 @@
         <v>45534</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76722,7 +76722,7 @@
         <v>45702</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -76795,7 +76795,7 @@
         <v>45219</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -76868,7 +76868,7 @@
         <v>46210</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -76946,7 +76946,7 @@
         <v>44676</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77024,7 +77024,7 @@
         <v>45121</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77097,7 +77097,7 @@
         <v>45121</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77170,7 +77170,7 @@
         <v>45121</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77243,7 +77243,7 @@
         <v>45440</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77316,7 +77316,7 @@
         <v>45645</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77389,7 +77389,7 @@
         <v>45692</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77462,7 +77462,7 @@
         <v>45028</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77535,7 +77535,7 @@
         <v>45777</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77613,7 +77613,7 @@
         <v>45777</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77691,7 +77691,7 @@
         <v>45194</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77764,7 +77764,7 @@
         <v>45547</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -77837,7 +77837,7 @@
         <v>45777</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -77915,7 +77915,7 @@
         <v>45519</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -77988,7 +77988,7 @@
         <v>45780</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78061,7 +78061,7 @@
         <v>45780</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78134,7 +78134,7 @@
         <v>45478</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78207,7 +78207,7 @@
         <v>45546</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78280,7 +78280,7 @@
         <v>45783</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78353,7 +78353,7 @@
         <v>45782</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78426,7 +78426,7 @@
         <v>45534</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78499,7 +78499,7 @@
         <v>44894</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78572,7 +78572,7 @@
         <v>45108</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78645,7 +78645,7 @@
         <v>44781</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78723,7 +78723,7 @@
         <v>45642</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78796,7 +78796,7 @@
         <v>46258</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -78869,7 +78869,7 @@
         <v>45614</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -78942,7 +78942,7 @@
         <v>45716</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79015,7 +79015,7 @@
         <v>45608</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79088,7 +79088,7 @@
         <v>46245</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79161,7 +79161,7 @@
         <v>46260</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79234,7 +79234,7 @@
         <v>46261</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79307,7 +79307,7 @@
         <v>45716</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79380,7 +79380,7 @@
         <v>45791</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79453,7 +79453,7 @@
         <v>46170</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79526,7 +79526,7 @@
         <v>46262</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79599,7 +79599,7 @@
         <v>46183</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79672,7 +79672,7 @@
         <v>46269</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79745,7 +79745,7 @@
         <v>46230</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -79818,7 +79818,7 @@
         <v>45054</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -79891,7 +79891,7 @@
         <v>45230</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -79969,7 +79969,7 @@
         <v>44498</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80042,7 +80042,7 @@
         <v>45622</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80115,7 +80115,7 @@
         <v>45054</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         <v>45054</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80261,7 +80261,7 @@
         <v>45056</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80334,7 +80334,7 @@
         <v>44715</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80407,7 +80407,7 @@
         <v>44722</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80480,7 +80480,7 @@
         <v>45434</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80553,7 +80553,7 @@
         <v>44468</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80626,7 +80626,7 @@
         <v>45054</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80699,7 +80699,7 @@
         <v>45407</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80772,7 +80772,7 @@
         <v>44802</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -80845,7 +80845,7 @@
         <v>45071</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -80918,7 +80918,7 @@
         <v>44495</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -80991,7 +80991,7 @@
         <v>44588</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81064,7 +81064,7 @@
         <v>44727</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81137,7 +81137,7 @@
         <v>44474</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81210,7 +81210,7 @@
         <v>45224</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81288,7 +81288,7 @@
         <v>44722</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81361,7 +81361,7 @@
         <v>44972</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81434,7 +81434,7 @@
         <v>44487</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81507,7 +81507,7 @@
         <v>45230</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81580,7 +81580,7 @@
         <v>44939</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81653,7 +81653,7 @@
         <v>45468</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81726,7 +81726,7 @@
         <v>45218</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81799,7 +81799,7 @@
         <v>45054</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -81872,7 +81872,7 @@
         <v>44603</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -81945,7 +81945,7 @@
         <v>44930</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82023,7 +82023,7 @@
         <v>44973</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82096,7 +82096,7 @@
         <v>44908</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82189,7 +82189,7 @@
         <v>44693</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82262,7 +82262,7 @@
         <v>44726</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82335,7 +82335,7 @@
         <v>45583</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82408,7 +82408,7 @@
         <v>45054</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82481,7 +82481,7 @@
         <v>44712</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82554,7 +82554,7 @@
         <v>45054</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82627,7 +82627,7 @@
         <v>44722</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82700,7 +82700,7 @@
         <v>44908</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82773,7 +82773,7 @@
         <v>44972</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -82846,7 +82846,7 @@
         <v>44978</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -82919,7 +82919,7 @@
         <v>44712</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -82992,7 +82992,7 @@
         <v>44887</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83065,7 +83065,7 @@
         <v>44704</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83138,7 +83138,7 @@
         <v>44909</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83211,7 +83211,7 @@
         <v>45408</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83284,7 +83284,7 @@
         <v>44596</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83357,7 +83357,7 @@
         <v>44908</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83430,7 +83430,7 @@
         <v>44704</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83503,7 +83503,7 @@
         <v>45054</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83576,7 +83576,7 @@
         <v>45526</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83649,7 +83649,7 @@
         <v>45436</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83722,7 +83722,7 @@
         <v>45485</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83795,7 +83795,7 @@
         <v>44588</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -83868,7 +83868,7 @@
         <v>45727</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>45740</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84014,7 +84014,7 @@
         <v>45726</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84087,7 +84087,7 @@
         <v>45797</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84160,7 +84160,7 @@
         <v>45805</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84233,7 +84233,7 @@
         <v>45831</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84306,7 +84306,7 @@
         <v>45951</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84379,7 +84379,7 @@
         <v>45958</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84452,7 +84452,7 @@
         <v>45964</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84525,7 +84525,7 @@
         <v>45965</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84598,7 +84598,7 @@
         <v>45981</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -84676,7 +84676,7 @@
         <v>45988</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -84749,7 +84749,7 @@
         <v>46092</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -84827,7 +84827,7 @@
         <v>46202</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -84900,7 +84900,7 @@
         <v>46262</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
